--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_PARTIZAN MOZZART BET BELGRADE.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_PARTIZAN MOZZART BET BELGRADE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA56"/>
+  <dimension ref="A1:BA54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -671,13 +671,13 @@
         <v>0.2056303549571603</v>
       </c>
       <c r="J2" t="n">
-        <v>389</v>
+        <v>15</v>
       </c>
       <c r="K2" t="n">
-        <v>387</v>
+        <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>307</v>
+        <v>14</v>
       </c>
       <c r="M2" t="n">
         <v>422</v>
@@ -752,13 +752,13 @@
         <v>1.023379383634431</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.790650406504065</v>
+        <v>0.03048780487804878</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.9897698209718671</v>
+        <v>0.01534526854219949</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.816568047337278</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="AN2" t="n">
         <v>1.397894736842105</v>
@@ -801,13 +801,13 @@
         <v>0.2056303549571603</v>
       </c>
       <c r="J3" t="n">
-        <v>10.23684210526316</v>
+        <v>0.3947368421052632</v>
       </c>
       <c r="K3" t="n">
-        <v>10.18421052631579</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="L3" t="n">
-        <v>8.078947368421053</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="M3" t="n">
         <v>11.10526315789474</v>
@@ -882,13 +882,13 @@
         <v>1.023379383634432</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.790650406504065</v>
+        <v>0.03048780487804878</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.9897698209718671</v>
+        <v>0.01534526854219949</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.816568047337278</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="AN3" t="n">
         <v>1.397894736842105</v>
@@ -931,16 +931,16 @@
         <v>0.2548770144189991</v>
       </c>
       <c r="J4" t="n">
-        <v>364</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>426</v>
+        <v>11</v>
       </c>
       <c r="L4" t="n">
-        <v>411</v>
+        <v>7</v>
       </c>
       <c r="M4" t="n">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="N4" t="n">
         <v>1116</v>
@@ -1012,13 +1012,13 @@
         <v>1.130260521042084</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.7663157894736842</v>
+        <v>0.01052631578947368</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.118110236220472</v>
+        <v>0.02887139107611549</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.663967611336032</v>
+        <v>1.75</v>
       </c>
       <c r="AN4" t="n">
         <v>1.502032520325203</v>
@@ -1061,16 +1061,16 @@
         <v>0.2548770144189991</v>
       </c>
       <c r="J5" t="n">
-        <v>9.578947368421053</v>
+        <v>0.131578947368421</v>
       </c>
       <c r="K5" t="n">
-        <v>11.21052631578947</v>
+        <v>0.2894736842105263</v>
       </c>
       <c r="L5" t="n">
-        <v>10.81578947368421</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M5" t="n">
-        <v>11.52631578947368</v>
+        <v>11.47368421052632</v>
       </c>
       <c r="N5" t="n">
         <v>29.36842105263158</v>
@@ -1142,13 +1142,13 @@
         <v>1.130260521042084</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.7663157894736843</v>
+        <v>0.01052631578947368</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.118110236220472</v>
+        <v>0.02887139107611549</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.663967611336032</v>
+        <v>1.75</v>
       </c>
       <c r="AN5" t="n">
         <v>1.502032520325203</v>
@@ -1486,16 +1486,16 @@
         <v>282</v>
       </c>
       <c r="U8" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>89</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>820:13</t>
+          <t>415:58</t>
         </is>
       </c>
       <c r="AO8" t="n">
@@ -1575,13 +1575,13 @@
         <v>9.111000000000001</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.135</v>
+        <v>0.266</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.018</v>
+        <v>0.036</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.051</v>
+        <v>0.101</v>
       </c>
       <c r="BA8" t="n">
         <v>0.065</v>
@@ -1651,16 +1651,16 @@
         <v>159</v>
       </c>
       <c r="U9" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="V9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>58</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>888:41</t>
+          <t>428:24</t>
         </is>
       </c>
       <c r="AO9" t="n">
@@ -1740,13 +1740,13 @@
         <v>6.333</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.098</v>
+        <v>0.203</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.014</v>
+        <v>0.03</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.029</v>
+        <v>0.06</v>
       </c>
       <c r="BA9" t="n">
         <v>0.052</v>
@@ -1819,7 +1819,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -1981,16 +1981,16 @@
         <v>292</v>
       </c>
       <c r="U11" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="n">
         <v>89</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>1020:30</t>
+          <t>504:24</t>
         </is>
       </c>
       <c r="AO11" t="n">
@@ -2070,13 +2070,13 @@
         <v>8.842000000000001</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.16</v>
+        <v>0.324</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.005</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.036</v>
+        <v>0.073</v>
       </c>
       <c r="BA11" t="n">
         <v>0.057</v>
@@ -2146,16 +2146,16 @@
         <v>278</v>
       </c>
       <c r="U12" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="V12" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="W12" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="X12" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
         <v>76</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>1356:13</t>
+          <t>697:31</t>
         </is>
       </c>
       <c r="AO12" t="n">
@@ -2235,13 +2235,13 @@
         <v>16.929</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.083</v>
+        <v>0.161</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.03</v>
+        <v>0.058</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.062</v>
+        <v>0.12</v>
       </c>
       <c r="BA12" t="n">
         <v>0.034</v>
@@ -2317,10 +2317,10 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
         <v>1</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>06:13</t>
         </is>
       </c>
       <c r="AO13" t="n">
@@ -2400,13 +2400,13 @@
         <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.03</v>
+        <v>0.077</v>
       </c>
       <c r="AY13" t="n">
         <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.076</v>
+        <v>0.198</v>
       </c>
       <c r="BA13" t="n">
         <v>0</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>29:25</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AO14" t="n">
@@ -2568,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.039</v>
+        <v>0.123</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
@@ -2641,16 +2641,16 @@
         <v>82</v>
       </c>
       <c r="U15" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>29</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>842:01</t>
+          <t>388:21</t>
         </is>
       </c>
       <c r="AO15" t="n">
@@ -2730,13 +2730,13 @@
         <v>10.545</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.068</v>
+        <v>0.148</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.01</v>
+        <v>0.021</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.035</v>
+        <v>0.076</v>
       </c>
       <c r="BA15" t="n">
         <v>0.014</v>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>22:13</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AO16" t="n">
@@ -2895,13 +2895,13 @@
         <v>1</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.043</v>
+        <v>0.079</v>
       </c>
       <c r="AY16" t="n">
         <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.055</v>
+        <v>0.101</v>
       </c>
       <c r="BA16" t="n">
         <v>0</v>
@@ -2971,16 +2971,16 @@
         <v>83</v>
       </c>
       <c r="U17" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>17</v>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>633:50</t>
+          <t>325:52</t>
         </is>
       </c>
       <c r="AO17" t="n">
@@ -3060,13 +3060,13 @@
         <v>9.25</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.164</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.02</v>
+        <v>0.039</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.17</v>
       </c>
       <c r="BA17" t="n">
         <v>0.012</v>
@@ -3136,16 +3136,16 @@
         <v>461</v>
       </c>
       <c r="U18" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>115</v>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>1969:01</t>
+          <t>1036:55</t>
         </is>
       </c>
       <c r="AO18" t="n">
@@ -3225,13 +3225,13 @@
         <v>6.587</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.125</v>
+        <v>0.237</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.012</v>
+        <v>0.023</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.053</v>
+        <v>0.1</v>
       </c>
       <c r="BA18" t="n">
         <v>0.089</v>
@@ -3304,13 +3304,13 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
         <v>2</v>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>207:15</t>
+          <t>68:17</t>
         </is>
       </c>
       <c r="AO19" t="n">
@@ -3390,13 +3390,13 @@
         <v>3.4</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.042</v>
+        <v>0.126</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.017</v>
+        <v>0.051</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.036</v>
+        <v>0.108</v>
       </c>
       <c r="BA19" t="n">
         <v>0.004</v>
@@ -3466,16 +3466,16 @@
         <v>121</v>
       </c>
       <c r="U20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W20" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="X20" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
         <v>36</v>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>434:19</t>
+          <t>233:21</t>
         </is>
       </c>
       <c r="AO20" t="n">
@@ -3555,13 +3555,13 @@
         <v>6.182</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.146</v>
+        <v>0.271</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.011</v>
+        <v>0.02</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.054</v>
+        <v>0.1</v>
       </c>
       <c r="BA20" t="n">
         <v>0.035</v>
@@ -3631,16 +3631,16 @@
         <v>563</v>
       </c>
       <c r="U21" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="X21" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
         <v>165</v>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>2008:53</t>
+          <t>1050:46</t>
         </is>
       </c>
       <c r="AO21" t="n">
@@ -3720,13 +3720,13 @@
         <v>6.625</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.163</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.036</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.092</v>
+        <v>0.176</v>
       </c>
       <c r="BA21" t="n">
         <v>0.056</v>
@@ -3796,16 +3796,16 @@
         <v>72</v>
       </c>
       <c r="U22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
         <v>12</v>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>813:34</t>
+          <t>326:26</t>
         </is>
       </c>
       <c r="AO22" t="n">
@@ -3885,13 +3885,13 @@
         <v>10.714</v>
       </c>
       <c r="AX22" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="AY22" t="n">
         <v>0.042</v>
       </c>
-      <c r="AY22" t="n">
-        <v>0.017</v>
-      </c>
       <c r="AZ22" t="n">
-        <v>0.045</v>
+        <v>0.113</v>
       </c>
       <c r="BA22" t="n">
         <v>0.013</v>
@@ -3961,16 +3961,16 @@
         <v>90</v>
       </c>
       <c r="U23" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
         <v>35</v>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>527:53</t>
+          <t>288:38</t>
         </is>
       </c>
       <c r="AO23" t="n">
@@ -4050,13 +4050,13 @@
         <v>9.231</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.119</v>
+        <v>0.218</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.024</v>
+        <v>0.044</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.063</v>
+        <v>0.115</v>
       </c>
       <c r="BA23" t="n">
         <v>0.008999999999999999</v>
@@ -4126,16 +4126,16 @@
         <v>159</v>
       </c>
       <c r="U24" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
         <v>34</v>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>558:27</t>
+          <t>289:08</t>
         </is>
       </c>
       <c r="AO24" t="n">
@@ -4215,13 +4215,13 @@
         <v>7.786</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.096</v>
+        <v>0.186</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.064</v>
+        <v>0.124</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.097</v>
+        <v>0.188</v>
       </c>
       <c r="BA24" t="n">
         <v>0.019</v>
@@ -4291,16 +4291,16 @@
         <v>367</v>
       </c>
       <c r="U25" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="X25" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
         <v>144</v>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>1168:04</t>
+          <t>588:38</t>
         </is>
       </c>
       <c r="AO25" t="n">
@@ -4380,13 +4380,13 @@
         <v>3.538</v>
       </c>
       <c r="AX25" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="AY25" t="n">
         <v>0.104</v>
       </c>
-      <c r="AY25" t="n">
-        <v>0.052</v>
-      </c>
       <c r="AZ25" t="n">
-        <v>0.094</v>
+        <v>0.186</v>
       </c>
       <c r="BA25" t="n">
         <v>0.02</v>
@@ -4456,16 +4456,16 @@
         <v>194</v>
       </c>
       <c r="U26" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="V26" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
         <v>29</v>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>1287:22</t>
+          <t>589:33</t>
         </is>
       </c>
       <c r="AO26" t="n">
@@ -4545,13 +4545,13 @@
         <v>6.133</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.073</v>
+        <v>0.16</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.012</v>
+        <v>0.025</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0.06</v>
+        <v>0.132</v>
       </c>
       <c r="BA26" t="n">
         <v>0.121</v>
@@ -4621,16 +4621,16 @@
         <v>287</v>
       </c>
       <c r="U27" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="W27" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
         <v>95</v>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>740:02</t>
+          <t>401:18</t>
         </is>
       </c>
       <c r="AO27" t="n">
@@ -4710,13 +4710,13 @@
         <v>5.444</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.104</v>
+        <v>0.191</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.064</v>
+        <v>0.118</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0.105</v>
+        <v>0.194</v>
       </c>
       <c r="BA27" t="n">
         <v>0.033</v>
@@ -4890,163 +4890,163 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>38</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>3101</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>817</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>1510</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>941</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>622</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>664</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>864</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>391</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>475</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>422</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>729</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>727</v>
       </c>
       <c r="T29" t="n">
-        <v>88</v>
+        <v>3578</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1027</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1311</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>0.783</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>589</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>0.413</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>0.447</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>0.422</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>839</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>0.331</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>7675:00</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>34</v>
+        <v>3199.68</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>0.569</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>0.969</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>0.148</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>0.206</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>1.398</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>6.558</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>0.139</v>
       </c>
       <c r="BA29" t="n">
         <v>0</v>
@@ -5055,44 +5055,44 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Rival</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>38</v>
       </c>
       <c r="C30" t="n">
-        <v>3101</v>
+        <v>3289</v>
       </c>
       <c r="D30" t="n">
-        <v>817</v>
+        <v>780</v>
       </c>
       <c r="E30" t="n">
-        <v>1510</v>
+        <v>1360</v>
       </c>
       <c r="F30" t="n">
-        <v>321</v>
+        <v>376</v>
       </c>
       <c r="G30" t="n">
-        <v>941</v>
+        <v>998</v>
       </c>
       <c r="H30" t="n">
-        <v>504</v>
+        <v>601</v>
       </c>
       <c r="I30" t="n">
-        <v>622</v>
+        <v>782</v>
       </c>
       <c r="J30" t="n">
-        <v>664</v>
+        <v>739</v>
       </c>
       <c r="K30" t="n">
-        <v>864</v>
+        <v>938</v>
       </c>
       <c r="L30" t="n">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="M30" t="n">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="N30" t="n">
         <v>196</v>
@@ -5101,76 +5101,76 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>475</v>
+        <v>492</v>
       </c>
       <c r="Q30" t="n">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="R30" t="n">
-        <v>729</v>
+        <v>662</v>
       </c>
       <c r="S30" t="n">
-        <v>727</v>
+        <v>792</v>
       </c>
       <c r="T30" t="n">
-        <v>3578</v>
+        <v>4050</v>
       </c>
       <c r="U30" t="n">
-        <v>389</v>
+        <v>5</v>
       </c>
       <c r="V30" t="n">
-        <v>387</v>
+        <v>11</v>
       </c>
       <c r="W30" t="n">
-        <v>307</v>
+        <v>7</v>
       </c>
       <c r="X30" t="n">
-        <v>169</v>
+        <v>4</v>
       </c>
       <c r="Y30" t="n">
-        <v>1027</v>
+        <v>1116</v>
       </c>
       <c r="Z30" t="n">
-        <v>1311</v>
+        <v>1318</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.783</v>
+        <v>0.847</v>
       </c>
       <c r="AB30" t="n">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="AC30" t="n">
-        <v>589</v>
+        <v>530</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.413</v>
+        <v>0.423</v>
       </c>
       <c r="AE30" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="AF30" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.447</v>
+        <v>0.363</v>
       </c>
       <c r="AH30" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="AI30" t="n">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.422</v>
+        <v>0.47</v>
       </c>
       <c r="AK30" t="n">
-        <v>278</v>
+        <v>345</v>
       </c>
       <c r="AL30" t="n">
-        <v>839</v>
+        <v>932</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.331</v>
+        <v>0.37</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
@@ -5178,40 +5178,40 @@
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>3199.68</v>
+        <v>3194.08</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.53</v>
+        <v>0.57</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.569</v>
+        <v>0.609</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.969</v>
+        <v>1.03</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.148</v>
+        <v>0.154</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.206</v>
+        <v>0.255</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.398</v>
+        <v>1.502</v>
       </c>
       <c r="AV30" t="n">
-        <v>5.16</v>
+        <v>4.793</v>
       </c>
       <c r="AW30" t="n">
-        <v>6.558</v>
+        <v>6.295</v>
       </c>
       <c r="AX30" t="n">
         <v>0.2</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.059</v>
+        <v>0.061</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0.139</v>
+        <v>0.141</v>
       </c>
       <c r="BA30" t="n">
         <v>0</v>
@@ -5220,325 +5220,325 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>38</v>
-      </c>
-      <c r="C31" t="n">
-        <v>3289</v>
-      </c>
-      <c r="D31" t="n">
-        <v>780</v>
-      </c>
-      <c r="E31" t="n">
-        <v>1360</v>
-      </c>
-      <c r="F31" t="n">
-        <v>376</v>
-      </c>
-      <c r="G31" t="n">
-        <v>998</v>
-      </c>
-      <c r="H31" t="n">
-        <v>601</v>
-      </c>
-      <c r="I31" t="n">
-        <v>782</v>
-      </c>
-      <c r="J31" t="n">
-        <v>739</v>
-      </c>
-      <c r="K31" t="n">
-        <v>938</v>
-      </c>
-      <c r="L31" t="n">
-        <v>381</v>
-      </c>
-      <c r="M31" t="n">
-        <v>252</v>
-      </c>
-      <c r="N31" t="n">
-        <v>196</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>492</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>438</v>
-      </c>
-      <c r="R31" t="n">
-        <v>662</v>
-      </c>
-      <c r="S31" t="n">
-        <v>792</v>
-      </c>
-      <c r="T31" t="n">
-        <v>4050</v>
-      </c>
-      <c r="U31" t="n">
-        <v>364</v>
-      </c>
-      <c r="V31" t="n">
-        <v>426</v>
-      </c>
-      <c r="W31" t="n">
-        <v>411</v>
-      </c>
-      <c r="X31" t="n">
-        <v>247</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1116</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1318</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0.847</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>224</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>530</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0.423</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>41</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>113</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0.363</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>31</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>66</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>345</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>932</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>7675:00</t>
-        </is>
-      </c>
-      <c r="AO31" t="n">
-        <v>3194.08</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0.609</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>1.502</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>4.793</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>6.295</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>0</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
+      <c r="AP31" t="inlineStr"/>
+      <c r="AQ31" t="inlineStr"/>
+      <c r="AR31" t="inlineStr"/>
+      <c r="AS31" t="inlineStr"/>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AU31" t="inlineStr"/>
+      <c r="AV31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr"/>
+      <c r="AX31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr"/>
+      <c r="BA31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
-      <c r="AB32" t="inlineStr"/>
-      <c r="AC32" t="inlineStr"/>
-      <c r="AD32" t="inlineStr"/>
-      <c r="AE32" t="inlineStr"/>
-      <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="inlineStr"/>
-      <c r="AH32" t="inlineStr"/>
-      <c r="AI32" t="inlineStr"/>
-      <c r="AJ32" t="inlineStr"/>
-      <c r="AK32" t="inlineStr"/>
-      <c r="AL32" t="inlineStr"/>
-      <c r="AM32" t="inlineStr"/>
-      <c r="AN32" t="inlineStr"/>
-      <c r="AO32" t="inlineStr"/>
-      <c r="AP32" t="inlineStr"/>
-      <c r="AQ32" t="inlineStr"/>
-      <c r="AR32" t="inlineStr"/>
-      <c r="AS32" t="inlineStr"/>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AU32" t="inlineStr"/>
-      <c r="AV32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr"/>
-      <c r="AX32" t="inlineStr"/>
-      <c r="AY32" t="inlineStr"/>
-      <c r="AZ32" t="inlineStr"/>
-      <c r="BA32" t="inlineStr"/>
+          <t>#1 C. JONES (Per Game)</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>15</v>
+      </c>
+      <c r="C32" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="D32" t="n">
+        <v>4.667</v>
+      </c>
+      <c r="E32" t="n">
+        <v>9</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="I32" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="J32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.267</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.267</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.867</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4</v>
+      </c>
+      <c r="T32" t="n">
+        <v>282</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>5.933</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.802</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.867</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.067</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="AN32" t="inlineStr">
+        <is>
+          <t>27:43</t>
+        </is>
+      </c>
+      <c r="AO32" t="n">
+        <v>15.389</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>2.556</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>6.556</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>9.111000000000001</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0.188</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>#1 C. JONES (Per Game)</t>
+          <t>#2 S. MILTON (Per Game)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C33" t="n">
-        <v>15.4</v>
+        <v>6.583</v>
       </c>
       <c r="D33" t="n">
-        <v>4.667</v>
+        <v>2.042</v>
       </c>
       <c r="E33" t="n">
-        <v>9</v>
+        <v>4.125</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8</v>
+        <v>0.375</v>
       </c>
       <c r="G33" t="n">
-        <v>2.8</v>
+        <v>1.458</v>
       </c>
       <c r="H33" t="n">
-        <v>3.667</v>
+        <v>1.375</v>
       </c>
       <c r="I33" t="n">
-        <v>4.067</v>
+        <v>1.625</v>
       </c>
       <c r="J33" t="n">
-        <v>4.6</v>
+        <v>2.333</v>
       </c>
       <c r="K33" t="n">
-        <v>2.267</v>
+        <v>0.875</v>
       </c>
       <c r="L33" t="n">
-        <v>0.867</v>
+        <v>0.458</v>
       </c>
       <c r="M33" t="n">
-        <v>0.8</v>
+        <v>0.458</v>
       </c>
       <c r="N33" t="n">
-        <v>1.267</v>
+        <v>0.542</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.667</v>
+        <v>1.167</v>
       </c>
       <c r="R33" t="n">
-        <v>1.867</v>
+        <v>1.958</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T33" t="n">
-        <v>282</v>
+        <v>159</v>
       </c>
       <c r="U33" t="n">
-        <v>2.067</v>
+        <v>0.167</v>
       </c>
       <c r="V33" t="n">
-        <v>0.9330000000000001</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>5.933</v>
+        <v>2.417</v>
       </c>
       <c r="Z33" t="n">
-        <v>7.4</v>
+        <v>3.25</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.802</v>
+        <v>0.744</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.867</v>
+        <v>0.958</v>
       </c>
       <c r="AC33" t="n">
-        <v>4.2</v>
+        <v>2.167</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.444</v>
+        <v>0.442</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.533</v>
+        <v>0.042</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.067</v>
+        <v>0.083</v>
       </c>
       <c r="AG33" t="n">
         <v>0.5</v>
@@ -5547,742 +5547,742 @@
         <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.2</v>
+        <v>0.083</v>
       </c>
       <c r="AJ33" t="n">
         <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.8</v>
+        <v>0.375</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.6</v>
+        <v>1.375</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.308</v>
+        <v>0.273</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>54:40</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>15.389</v>
+        <v>7.548</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.497</v>
+        <v>0.466</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.523</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.001</v>
+        <v>0.872</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.117</v>
+        <v>0.166</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.311</v>
+        <v>0.246</v>
       </c>
       <c r="AU33" t="n">
-        <v>2.556</v>
+        <v>1.867</v>
       </c>
       <c r="AV33" t="n">
-        <v>6.556</v>
+        <v>4.467</v>
       </c>
       <c r="AW33" t="n">
-        <v>9.111000000000001</v>
+        <v>6.333</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.135</v>
+        <v>0.203</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.018</v>
+        <v>0.03</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.051</v>
+        <v>0.06</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.188</v>
+        <v>0.08500000000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#2 S. MILTON (Per Game)</t>
+          <t>#3 M. MUURINEN (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C34" t="n">
-        <v>6.583</v>
+        <v>0.062</v>
       </c>
       <c r="D34" t="n">
-        <v>2.042</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>4.125</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>1.458</v>
+        <v>0.062</v>
       </c>
       <c r="H34" t="n">
-        <v>1.375</v>
+        <v>0.062</v>
       </c>
       <c r="I34" t="n">
-        <v>1.625</v>
+        <v>0.125</v>
       </c>
       <c r="J34" t="n">
-        <v>2.333</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0.458</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.458</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0.542</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.167</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.958</v>
+        <v>0.062</v>
       </c>
       <c r="S34" t="n">
-        <v>2</v>
+        <v>0.125</v>
       </c>
       <c r="T34" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.417</v>
+        <v>0.062</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.25</v>
+        <v>0.062</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.744</v>
+        <v>1</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.958</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.167</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.442</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.042</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
         <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
         <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.375</v>
+        <v>0.062</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.273</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>37:01</t>
+          <t>00:41</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>7.548</v>
+        <v>0.118</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.466</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.523</v>
+        <v>0.266</v>
       </c>
       <c r="AR34" t="n">
-        <v>0.872</v>
+        <v>0.532</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.166</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.246</v>
+        <v>1</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.867</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>4.467</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>6.333</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.098</v>
+        <v>0.082</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>0.08500000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#3 M. MUURINEN (Per Game)</t>
+          <t>#4 D. WASHINGTON (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C35" t="n">
-        <v>0.062</v>
+        <v>14.292</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>3.167</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>6.167</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>2.042</v>
       </c>
       <c r="G35" t="n">
-        <v>0.062</v>
+        <v>5.417</v>
       </c>
       <c r="H35" t="n">
-        <v>0.062</v>
+        <v>1.833</v>
       </c>
       <c r="I35" t="n">
+        <v>2.292</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.583</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.583</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2.083</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.208</v>
+      </c>
+      <c r="T35" t="n">
+        <v>292</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>3.708</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>4.917</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="AH35" t="n">
         <v>0.125</v>
       </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>0</v>
-      </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.917</v>
       </c>
       <c r="AL35" t="n">
-        <v>0.062</v>
+        <v>5.083</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>0.377</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>00:41</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>0.118</v>
+        <v>14.175</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>0.538</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.266</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AR35" t="n">
-        <v>0.532</v>
+        <v>1.008</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>0.112</v>
       </c>
       <c r="AT35" t="n">
-        <v>1</v>
+        <v>0.158</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>1.526</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>7.316</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>8.842000000000001</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.082</v>
+        <v>0.324</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>0.073</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>#4 D. WASHINGTON (Per Game)</t>
+          <t>#5 D. OSETKOWSKI (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="C36" t="n">
-        <v>14.292</v>
+        <v>6.811</v>
       </c>
       <c r="D36" t="n">
-        <v>3.167</v>
+        <v>1.351</v>
       </c>
       <c r="E36" t="n">
-        <v>6.167</v>
+        <v>2.568</v>
       </c>
       <c r="F36" t="n">
-        <v>2.042</v>
+        <v>1.027</v>
       </c>
       <c r="G36" t="n">
-        <v>5.417</v>
+        <v>2.865</v>
       </c>
       <c r="H36" t="n">
-        <v>1.833</v>
+        <v>1.027</v>
       </c>
       <c r="I36" t="n">
-        <v>2.292</v>
+        <v>1.162</v>
       </c>
       <c r="J36" t="n">
-        <v>2.417</v>
+        <v>0.973</v>
       </c>
       <c r="K36" t="n">
-        <v>1.25</v>
+        <v>1.838</v>
       </c>
       <c r="L36" t="n">
-        <v>0.167</v>
+        <v>0.946</v>
       </c>
       <c r="M36" t="n">
-        <v>0.583</v>
+        <v>0.946</v>
       </c>
       <c r="N36" t="n">
-        <v>0.75</v>
+        <v>0.351</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.583</v>
+        <v>0.378</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.583</v>
+        <v>0.378</v>
       </c>
       <c r="R36" t="n">
-        <v>2.083</v>
+        <v>1.919</v>
       </c>
       <c r="S36" t="n">
-        <v>3.208</v>
+        <v>1.135</v>
       </c>
       <c r="T36" t="n">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="U36" t="n">
-        <v>2.667</v>
+        <v>0.189</v>
       </c>
       <c r="V36" t="n">
-        <v>0.833</v>
+        <v>0.054</v>
       </c>
       <c r="W36" t="n">
-        <v>1.5</v>
+        <v>0.081</v>
       </c>
       <c r="X36" t="n">
-        <v>0.583</v>
+        <v>0.027</v>
       </c>
       <c r="Y36" t="n">
-        <v>3.708</v>
+        <v>2.054</v>
       </c>
       <c r="Z36" t="n">
-        <v>4.917</v>
+        <v>2.676</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.754</v>
+        <v>0.768</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.958</v>
+        <v>0.243</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.375</v>
+        <v>0.73</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.404</v>
+        <v>0.333</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.333</v>
+        <v>0.081</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.708</v>
+        <v>0.189</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.471</v>
+        <v>0.429</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.125</v>
+        <v>0.189</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.333</v>
+        <v>0.486</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.375</v>
+        <v>0.389</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.917</v>
+        <v>0.838</v>
       </c>
       <c r="AL36" t="n">
-        <v>5.083</v>
+        <v>2.378</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.377</v>
+        <v>0.352</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>42:31</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>14.175</v>
+        <v>6.322</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.538</v>
+        <v>0.532</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.573</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.008</v>
+        <v>1.077</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.112</v>
+        <v>0.06</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.158</v>
+        <v>0.189</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.526</v>
+        <v>2.571</v>
       </c>
       <c r="AV36" t="n">
-        <v>7.316</v>
+        <v>14.357</v>
       </c>
       <c r="AW36" t="n">
-        <v>8.842000000000001</v>
+        <v>16.929</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.16</v>
+        <v>0.161</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.005</v>
+        <v>0.058</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0.036</v>
+        <v>0.12</v>
       </c>
       <c r="BA36" t="n">
-        <v>0.098</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>#5 D. OSETKOWSKI (Per Game)</t>
+          <t>#7 M. NAKIC (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>6.811</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>1.351</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>2.568</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>1.027</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>2.865</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.027</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>1.162</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0.973</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>1.838</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>0.946</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.946</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0.351</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.378</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.378</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.919</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>1.135</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>278</v>
+        <v>3</v>
       </c>
       <c r="U37" t="n">
-        <v>0.865</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
         <v>1</v>
       </c>
-      <c r="W37" t="n">
-        <v>0.757</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0.432</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>2.054</v>
-      </c>
       <c r="Z37" t="n">
-        <v>2.676</v>
+        <v>1</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.768</v>
+        <v>1</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.243</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.73</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.081</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.189</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.429</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.189</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.486</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.389</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.838</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>2.378</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.352</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>36:39</t>
+          <t>06:13</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>6.322</v>
+        <v>1</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.532</v>
+        <v>1</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.573</v>
+        <v>1</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.077</v>
+        <v>2</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.189</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.571</v>
+        <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>14.357</v>
+        <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>16.929</v>
+        <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.083</v>
+        <v>0.077</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0.062</v>
+        <v>0.198</v>
       </c>
       <c r="BA37" t="n">
-        <v>0.035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>#7 M. NAKIC (Per Game)</t>
+          <t>#8 M. BOSNJAKOVIC (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -6300,10 +6300,10 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -6321,13 +6321,13 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -6336,19 +6336,19 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
         <v>0</v>
@@ -6388,20 +6388,20 @@
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>00:23</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AS38" t="n">
         <v>0</v>
@@ -6419,13 +6419,13 @@
         <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>0.123</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0.076</v>
+        <v>0</v>
       </c>
       <c r="BA38" t="n">
         <v>0</v>
@@ -6434,65 +6434,65 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>#8 M. BOSNJAKOVIC (Per Game)</t>
+          <t>#9 V. MARINKOVIC (Per Game)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>5.947</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>0.789</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>1.684</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>1.211</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>3.632</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>0.737</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>0.947</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>0.789</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>1.263</v>
       </c>
       <c r="L39" t="n">
-        <v>0.042</v>
+        <v>0.368</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>0.526</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>0.579</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>0.579</v>
       </c>
       <c r="R39" t="n">
-        <v>0.042</v>
+        <v>1.579</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.053</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -6507,19 +6507,19 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.526</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>0.763</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>0.316</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -6528,163 +6528,163 @@
         <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>0.105</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>0.211</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.158</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>3.421</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>0.338</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>01:13</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>0</v>
+        <v>6.312</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>0.519</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>0.092</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>0.139</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>1.364</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>9.182</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>10.545</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>0.148</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.039</v>
+        <v>0.021</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>0.076</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>#9 V. MARINKOVIC (Per Game)</t>
+          <t>#10 U. MIJAILOVIC (Per Game)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C40" t="n">
-        <v>5.947</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0.789</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>1.684</v>
+        <v>0.083</v>
       </c>
       <c r="F40" t="n">
-        <v>1.211</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>3.632</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.737</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0.947</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0.789</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>1.263</v>
+        <v>0.083</v>
       </c>
       <c r="L40" t="n">
-        <v>0.368</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.526</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>0.053</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0.579</v>
+        <v>0.083</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.579</v>
+        <v>0.083</v>
       </c>
       <c r="R40" t="n">
-        <v>1.579</v>
+        <v>0.417</v>
       </c>
       <c r="S40" t="n">
-        <v>1.053</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>82</v>
+        <v>-6</v>
       </c>
       <c r="U40" t="n">
-        <v>0.579</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.105</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>0.737</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0.368</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.526</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.763</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.316</v>
+        <v>0.083</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -6693,136 +6693,136 @@
         <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.105</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.053</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.211</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.158</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>3.421</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.338</v>
+        <v>0</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>44:19</t>
+          <t>01:01</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>6.312</v>
+        <v>0.167</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.49</v>
+        <v>0</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.519</v>
+        <v>0</v>
       </c>
       <c r="AR40" t="n">
-        <v>0.9419999999999999</v>
+        <v>0</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.092</v>
+        <v>0.5</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.139</v>
+        <v>0</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.364</v>
+        <v>0</v>
       </c>
       <c r="AV40" t="n">
-        <v>9.182</v>
+        <v>1</v>
       </c>
       <c r="AW40" t="n">
-        <v>10.545</v>
+        <v>1</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.068</v>
+        <v>0.079</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0.035</v>
+        <v>0.101</v>
       </c>
       <c r="BA40" t="n">
-        <v>0.028</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>#10 U. MIJAILOVIC (Per Game)</t>
+          <t>#11 A. POKUSEVSKI (Per Game)</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>3.125</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="E41" t="n">
-        <v>0.083</v>
+        <v>1.5</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>0.469</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1.562</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>0.094</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>0.094</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>0.406</v>
       </c>
       <c r="K41" t="n">
-        <v>0.083</v>
+        <v>1.406</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>0.344</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>0.344</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>0.312</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0.083</v>
+        <v>0.375</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.083</v>
+        <v>0.375</v>
       </c>
       <c r="R41" t="n">
-        <v>0.417</v>
+        <v>1.344</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>0.156</v>
       </c>
       <c r="T41" t="n">
-        <v>-6</v>
+        <v>83</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -6837,1351 +6837,1351 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>0.531</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>0.781</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>0.344</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.083</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>0.312</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>0.406</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>0.325</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>01:51</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>0.167</v>
+        <v>3.479</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>0.495</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>0.503</v>
       </c>
       <c r="AR41" t="n">
-        <v>0</v>
+        <v>0.898</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.5</v>
+        <v>0.108</v>
       </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="AU41" t="n">
-        <v>0</v>
+        <v>1.083</v>
       </c>
       <c r="AV41" t="n">
-        <v>1</v>
+        <v>8.167</v>
       </c>
       <c r="AW41" t="n">
-        <v>1</v>
+        <v>9.25</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.043</v>
+        <v>0.164</v>
       </c>
       <c r="AY41" t="n">
-        <v>0</v>
+        <v>0.039</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0.055</v>
+        <v>0.17</v>
       </c>
       <c r="BA41" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>#11 A. POKUSEVSKI (Per Game)</t>
+          <t>#12 S. BROWN (Per Game)</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C42" t="n">
-        <v>3.125</v>
+        <v>13.703</v>
       </c>
       <c r="D42" t="n">
-        <v>0.8120000000000001</v>
+        <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>1.5</v>
+        <v>5.811</v>
       </c>
       <c r="F42" t="n">
-        <v>0.469</v>
+        <v>2.054</v>
       </c>
       <c r="G42" t="n">
-        <v>1.562</v>
+        <v>5.243</v>
       </c>
       <c r="H42" t="n">
-        <v>0.094</v>
+        <v>1.541</v>
       </c>
       <c r="I42" t="n">
-        <v>0.094</v>
+        <v>1.703</v>
       </c>
       <c r="J42" t="n">
-        <v>0.406</v>
+        <v>2.297</v>
       </c>
       <c r="K42" t="n">
-        <v>1.406</v>
+        <v>2.27</v>
       </c>
       <c r="L42" t="n">
-        <v>0.344</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="M42" t="n">
-        <v>0.344</v>
+        <v>0.892</v>
       </c>
       <c r="N42" t="n">
-        <v>0.312</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0.375</v>
+        <v>2.027</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.375</v>
+        <v>1.865</v>
       </c>
       <c r="R42" t="n">
-        <v>1.344</v>
+        <v>1.622</v>
       </c>
       <c r="S42" t="n">
-        <v>0.156</v>
+        <v>1.73</v>
       </c>
       <c r="T42" t="n">
-        <v>83</v>
+        <v>461</v>
       </c>
       <c r="U42" t="n">
-        <v>0.656</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0.312</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>0.062</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0.031</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.531</v>
+        <v>3.108</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.781</v>
+        <v>4.243</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.68</v>
+        <v>0.732</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.344</v>
+        <v>1.135</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.6879999999999999</v>
+        <v>2.432</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.5</v>
+        <v>0.467</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.031</v>
+        <v>0.297</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.125</v>
+        <v>0.676</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.25</v>
+        <v>0.44</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.062</v>
+        <v>0.459</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.312</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.2</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AK42" t="n">
-        <v>0.406</v>
+        <v>1.595</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.25</v>
+        <v>4.432</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.325</v>
+        <v>0.36</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>28:01</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>3.479</v>
+        <v>13.83</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.495</v>
+        <v>0.55</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.503</v>
+        <v>0.58</v>
       </c>
       <c r="AR42" t="n">
-        <v>0.898</v>
+        <v>0.991</v>
       </c>
       <c r="AS42" t="n">
-        <v>0.108</v>
+        <v>0.147</v>
       </c>
       <c r="AT42" t="n">
-        <v>0.031</v>
+        <v>0.139</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.083</v>
+        <v>1.133</v>
       </c>
       <c r="AV42" t="n">
-        <v>8.167</v>
+        <v>5.453</v>
       </c>
       <c r="AW42" t="n">
-        <v>9.25</v>
+        <v>6.587</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.237</v>
       </c>
       <c r="AY42" t="n">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="BA42" t="n">
-        <v>0.014</v>
+        <v>0.092</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>#12 S. BROWN (Per Game)</t>
+          <t>#13 A. RADANOV (Per Game)</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C43" t="n">
-        <v>13.703</v>
+        <v>0.923</v>
       </c>
       <c r="D43" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="T43" t="n">
         <v>3</v>
       </c>
-      <c r="E43" t="n">
-        <v>5.811</v>
-      </c>
-      <c r="F43" t="n">
-        <v>2.054</v>
-      </c>
-      <c r="G43" t="n">
-        <v>5.243</v>
-      </c>
-      <c r="H43" t="n">
-        <v>1.541</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1.703</v>
-      </c>
-      <c r="J43" t="n">
-        <v>2.297</v>
-      </c>
-      <c r="K43" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0.5679999999999999</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0.892</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0.8110000000000001</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>2.027</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>1.865</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.622</v>
-      </c>
-      <c r="S43" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="T43" t="n">
-        <v>461</v>
-      </c>
       <c r="U43" t="n">
-        <v>2.054</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.378</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.595</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0.865</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>3.108</v>
+        <v>0.154</v>
       </c>
       <c r="Z43" t="n">
-        <v>4.243</v>
+        <v>0.154</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.732</v>
+        <v>1</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.135</v>
+        <v>0.077</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.432</v>
+        <v>0.231</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.467</v>
+        <v>0.333</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.297</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.676</v>
+        <v>0.077</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.459</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.077</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.5669999999999999</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.595</v>
+        <v>0.154</v>
       </c>
       <c r="AL43" t="n">
-        <v>4.432</v>
+        <v>0.462</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.36</v>
+        <v>0.333</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>53:13</t>
+          <t>05:15</t>
         </is>
       </c>
       <c r="AO43" t="n">
-        <v>13.83</v>
+        <v>1.385</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.55</v>
+        <v>0.462</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.58</v>
+        <v>0.462</v>
       </c>
       <c r="AR43" t="n">
-        <v>0.991</v>
+        <v>0.667</v>
       </c>
       <c r="AS43" t="n">
-        <v>0.147</v>
+        <v>0.278</v>
       </c>
       <c r="AT43" t="n">
-        <v>0.139</v>
+        <v>0</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.133</v>
+        <v>0.8</v>
       </c>
       <c r="AV43" t="n">
-        <v>5.453</v>
+        <v>2.6</v>
       </c>
       <c r="AW43" t="n">
-        <v>6.587</v>
+        <v>3.4</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.125</v>
+        <v>0.126</v>
       </c>
       <c r="AY43" t="n">
-        <v>0.012</v>
+        <v>0.051</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0.053</v>
+        <v>0.108</v>
       </c>
       <c r="BA43" t="n">
-        <v>0.092</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>#13 A. RADANOV (Per Game)</t>
+          <t>#15 C. PAYNE (Per Game)</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C44" t="n">
-        <v>0.923</v>
+        <v>12.4</v>
       </c>
       <c r="D44" t="n">
-        <v>0.231</v>
+        <v>1.8</v>
       </c>
       <c r="E44" t="n">
-        <v>0.462</v>
+        <v>3.4</v>
       </c>
       <c r="F44" t="n">
-        <v>0.154</v>
+        <v>2.1</v>
       </c>
       <c r="G44" t="n">
-        <v>0.538</v>
+        <v>6.3</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="J44" t="n">
-        <v>0.308</v>
+        <v>3.9</v>
       </c>
       <c r="K44" t="n">
-        <v>0.462</v>
+        <v>1.9</v>
       </c>
       <c r="L44" t="n">
-        <v>0.231</v>
+        <v>0.4</v>
       </c>
       <c r="M44" t="n">
-        <v>0.077</v>
+        <v>1.2</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R44" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T44" t="n">
+        <v>121</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD44" t="n">
         <v>0.385</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.154</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="T44" t="n">
-        <v>3</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="W44" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="X44" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>0.333</v>
-      </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.077</v>
+        <v>0.4</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AH44" t="n">
         <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>0.077</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="n">
         <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>0.154</v>
+        <v>2.1</v>
       </c>
       <c r="AL44" t="n">
-        <v>0.462</v>
+        <v>6.3</v>
       </c>
       <c r="AM44" t="n">
         <v>0.333</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>1.385</v>
+        <v>13.176</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.462</v>
+        <v>0.51</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.462</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AR44" t="n">
-        <v>0.667</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="AS44" t="n">
-        <v>0.278</v>
+        <v>0.167</v>
       </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>0.258</v>
       </c>
       <c r="AU44" t="n">
-        <v>0.8</v>
+        <v>1.773</v>
       </c>
       <c r="AV44" t="n">
-        <v>2.6</v>
+        <v>4.409</v>
       </c>
       <c r="AW44" t="n">
-        <v>3.4</v>
+        <v>6.182</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.042</v>
+        <v>0.271</v>
       </c>
       <c r="AY44" t="n">
-        <v>0.017</v>
+        <v>0.02</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0.036</v>
+        <v>0.1</v>
       </c>
       <c r="BA44" t="n">
-        <v>0.01</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>#15 C. PAYNE (Per Game)</t>
+          <t>#17 I. BONGA (Per Game)</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="C45" t="n">
-        <v>12.4</v>
+        <v>9.946999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>1.8</v>
+        <v>2.553</v>
       </c>
       <c r="E45" t="n">
-        <v>3.4</v>
+        <v>4.237</v>
       </c>
       <c r="F45" t="n">
-        <v>2.1</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="G45" t="n">
-        <v>6.3</v>
+        <v>2.632</v>
       </c>
       <c r="H45" t="n">
-        <v>2.5</v>
+        <v>2.395</v>
       </c>
       <c r="I45" t="n">
-        <v>2.9</v>
+        <v>2.895</v>
       </c>
       <c r="J45" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="K45" t="n">
-        <v>1.9</v>
+        <v>3.947</v>
       </c>
       <c r="L45" t="n">
-        <v>0.4</v>
+        <v>1.658</v>
       </c>
       <c r="M45" t="n">
-        <v>1.2</v>
+        <v>0.921</v>
       </c>
       <c r="N45" t="n">
-        <v>0.5</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.2</v>
+        <v>1.263</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.1</v>
+        <v>1.158</v>
       </c>
       <c r="R45" t="n">
-        <v>2.6</v>
+        <v>1.921</v>
       </c>
       <c r="S45" t="n">
-        <v>2.8</v>
+        <v>3.342</v>
       </c>
       <c r="T45" t="n">
-        <v>121</v>
+        <v>563</v>
       </c>
       <c r="U45" t="n">
-        <v>0.8</v>
+        <v>0.053</v>
       </c>
       <c r="V45" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.9</v>
+        <v>0.053</v>
       </c>
       <c r="X45" t="n">
-        <v>0.9</v>
+        <v>0.026</v>
       </c>
       <c r="Y45" t="n">
-        <v>3.6</v>
+        <v>4.342</v>
       </c>
       <c r="Z45" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.857</v>
+        <v>0.868</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.5</v>
+        <v>0.579</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.3</v>
+        <v>1.553</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.385</v>
+        <v>0.373</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.2</v>
+        <v>0.026</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.4</v>
+        <v>0.079</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>0.132</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>0.237</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>0.556</v>
       </c>
       <c r="AK45" t="n">
-        <v>2.1</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="AL45" t="n">
-        <v>6.3</v>
+        <v>2.395</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.333</v>
+        <v>0.286</v>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>43:25</t>
+          <t>27:39</t>
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>13.176</v>
+        <v>9.404999999999999</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.51</v>
+        <v>0.55</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.611</v>
       </c>
       <c r="AR45" t="n">
-        <v>0.9409999999999999</v>
+        <v>1.058</v>
       </c>
       <c r="AS45" t="n">
-        <v>0.167</v>
+        <v>0.134</v>
       </c>
       <c r="AT45" t="n">
-        <v>0.258</v>
+        <v>0.349</v>
       </c>
       <c r="AU45" t="n">
-        <v>1.773</v>
+        <v>1.188</v>
       </c>
       <c r="AV45" t="n">
-        <v>4.409</v>
+        <v>5.438</v>
       </c>
       <c r="AW45" t="n">
-        <v>6.182</v>
+        <v>6.625</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.146</v>
+        <v>0.163</v>
       </c>
       <c r="AY45" t="n">
-        <v>0.011</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0.054</v>
+        <v>0.176</v>
       </c>
       <c r="BA45" t="n">
-        <v>0.15</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>#17 I. BONGA (Per Game)</t>
+          <t>#19 A. LAKIC (Per Game)</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C46" t="n">
-        <v>9.946999999999999</v>
+        <v>2.156</v>
       </c>
       <c r="D46" t="n">
-        <v>2.553</v>
+        <v>0.281</v>
       </c>
       <c r="E46" t="n">
-        <v>4.237</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="F46" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.469</v>
       </c>
       <c r="G46" t="n">
-        <v>2.632</v>
+        <v>1.344</v>
       </c>
       <c r="H46" t="n">
-        <v>2.395</v>
+        <v>0.188</v>
       </c>
       <c r="I46" t="n">
-        <v>2.895</v>
+        <v>0.25</v>
       </c>
       <c r="J46" t="n">
-        <v>1.5</v>
+        <v>0.438</v>
       </c>
       <c r="K46" t="n">
-        <v>3.947</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>1.658</v>
+        <v>0.375</v>
       </c>
       <c r="M46" t="n">
-        <v>0.921</v>
+        <v>0.469</v>
       </c>
       <c r="N46" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.094</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1.263</v>
+        <v>0.219</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.158</v>
+        <v>0.219</v>
       </c>
       <c r="R46" t="n">
-        <v>1.921</v>
+        <v>1.219</v>
       </c>
       <c r="S46" t="n">
-        <v>3.342</v>
+        <v>0.438</v>
       </c>
       <c r="T46" t="n">
-        <v>563</v>
+        <v>72</v>
       </c>
       <c r="U46" t="n">
-        <v>1.105</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.763</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.289</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>0.868</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>4.342</v>
+        <v>0.375</v>
       </c>
       <c r="Z46" t="n">
-        <v>5</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.868</v>
+        <v>0.667</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.579</v>
+        <v>0.094</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.553</v>
+        <v>0.125</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.373</v>
+        <v>0.75</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.079</v>
+        <v>0.062</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.132</v>
+        <v>0.031</v>
       </c>
       <c r="AI46" t="n">
-        <v>0.237</v>
+        <v>0.125</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0.556</v>
+        <v>0.25</v>
       </c>
       <c r="AK46" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.438</v>
       </c>
       <c r="AL46" t="n">
-        <v>2.395</v>
+        <v>1.219</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.286</v>
+        <v>0.359</v>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>52:51</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AO46" t="n">
-        <v>9.404999999999999</v>
+        <v>2.235</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.55</v>
+        <v>0.516</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.611</v>
+        <v>0.535</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.058</v>
+        <v>0.965</v>
       </c>
       <c r="AS46" t="n">
-        <v>0.134</v>
+        <v>0.098</v>
       </c>
       <c r="AT46" t="n">
-        <v>0.349</v>
+        <v>0.098</v>
       </c>
       <c r="AU46" t="n">
-        <v>1.188</v>
+        <v>2</v>
       </c>
       <c r="AV46" t="n">
-        <v>5.438</v>
+        <v>8.714</v>
       </c>
       <c r="AW46" t="n">
-        <v>6.625</v>
+        <v>10.714</v>
       </c>
       <c r="AX46" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.105</v>
       </c>
       <c r="AY46" t="n">
-        <v>0.036</v>
+        <v>0.042</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0.092</v>
+        <v>0.113</v>
       </c>
       <c r="BA46" t="n">
-        <v>0.056</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>#19 A. LAKIC (Per Game)</t>
+          <t>#22 J. PARKER (Per Game)</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C47" t="n">
-        <v>2.156</v>
+        <v>6.105</v>
       </c>
       <c r="D47" t="n">
-        <v>0.281</v>
+        <v>1.632</v>
       </c>
       <c r="E47" t="n">
-        <v>0.5620000000000001</v>
+        <v>3.632</v>
       </c>
       <c r="F47" t="n">
-        <v>0.469</v>
+        <v>0.632</v>
       </c>
       <c r="G47" t="n">
-        <v>1.344</v>
+        <v>2.158</v>
       </c>
       <c r="H47" t="n">
-        <v>0.188</v>
+        <v>0.947</v>
       </c>
       <c r="I47" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>0.438</v>
+        <v>0.526</v>
       </c>
       <c r="K47" t="n">
-        <v>0.9379999999999999</v>
+        <v>1.421</v>
       </c>
       <c r="L47" t="n">
-        <v>0.375</v>
+        <v>0.579</v>
       </c>
       <c r="M47" t="n">
-        <v>0.469</v>
+        <v>0.211</v>
       </c>
       <c r="N47" t="n">
-        <v>0.094</v>
+        <v>0.316</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>0.219</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.219</v>
+        <v>0.632</v>
       </c>
       <c r="R47" t="n">
-        <v>1.219</v>
+        <v>1.421</v>
       </c>
       <c r="S47" t="n">
-        <v>0.438</v>
+        <v>1.263</v>
       </c>
       <c r="T47" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="U47" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>0.188</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>0.094</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.375</v>
+        <v>1.842</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.5620000000000001</v>
+        <v>2.316</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.667</v>
+        <v>0.795</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.094</v>
+        <v>0.632</v>
       </c>
       <c r="AC47" t="n">
-        <v>0.125</v>
+        <v>1.947</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.75</v>
+        <v>0.324</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>0.105</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.062</v>
+        <v>0.316</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.031</v>
+        <v>0.211</v>
       </c>
       <c r="AI47" t="n">
-        <v>0.125</v>
+        <v>0.263</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AK47" t="n">
-        <v>0.438</v>
+        <v>0.421</v>
       </c>
       <c r="AL47" t="n">
-        <v>1.219</v>
+        <v>1.895</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.359</v>
+        <v>0.222</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>25:25</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>2.235</v>
+        <v>6.914</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.516</v>
+        <v>0.445</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.535</v>
+        <v>0.49</v>
       </c>
       <c r="AR47" t="n">
-        <v>0.965</v>
+        <v>0.883</v>
       </c>
       <c r="AS47" t="n">
-        <v>0.098</v>
+        <v>0.099</v>
       </c>
       <c r="AT47" t="n">
-        <v>0.098</v>
+        <v>0.164</v>
       </c>
       <c r="AU47" t="n">
-        <v>2</v>
+        <v>0.769</v>
       </c>
       <c r="AV47" t="n">
-        <v>8.714</v>
+        <v>8.462</v>
       </c>
       <c r="AW47" t="n">
-        <v>10.714</v>
+        <v>9.231</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.042</v>
+        <v>0.218</v>
       </c>
       <c r="AY47" t="n">
-        <v>0.017</v>
+        <v>0.044</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0.045</v>
+        <v>0.115</v>
       </c>
       <c r="BA47" t="n">
-        <v>0.015</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>#22 J. PARKER (Per Game)</t>
+          <t>#23 T. JEKIRI (Per Game)</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C48" t="n">
-        <v>6.105</v>
+        <v>7.467</v>
       </c>
       <c r="D48" t="n">
-        <v>1.632</v>
+        <v>3.2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.632</v>
+        <v>5.867</v>
       </c>
       <c r="F48" t="n">
-        <v>0.632</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>2.158</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.947</v>
+        <v>1.067</v>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>1.533</v>
       </c>
       <c r="J48" t="n">
-        <v>0.526</v>
+        <v>1.4</v>
       </c>
       <c r="K48" t="n">
-        <v>1.421</v>
+        <v>2.933</v>
       </c>
       <c r="L48" t="n">
-        <v>0.579</v>
+        <v>2.067</v>
       </c>
       <c r="M48" t="n">
-        <v>0.211</v>
+        <v>0.733</v>
       </c>
       <c r="N48" t="n">
-        <v>0.316</v>
+        <v>0.6</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.632</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="R48" t="n">
-        <v>1.421</v>
+        <v>2.533</v>
       </c>
       <c r="S48" t="n">
-        <v>1.263</v>
+        <v>2</v>
       </c>
       <c r="T48" t="n">
-        <v>90</v>
+        <v>159</v>
       </c>
       <c r="U48" t="n">
-        <v>0.579</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>0.316</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>0.368</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>0.211</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.842</v>
+        <v>2.267</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.316</v>
+        <v>2.8</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.795</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.632</v>
+        <v>1.333</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.947</v>
+        <v>3.2</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.324</v>
+        <v>0.417</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.105</v>
+        <v>0.667</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.316</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.333</v>
+        <v>0.714</v>
       </c>
       <c r="AH48" t="n">
-        <v>0.211</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
-        <v>0.263</v>
+        <v>0</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>0.421</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
-        <v>1.895</v>
+        <v>0</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.222</v>
+        <v>0</v>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>27:47</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AO48" t="n">
-        <v>6.914</v>
+        <v>7.475</v>
       </c>
       <c r="AP48" t="n">
-        <v>0.445</v>
+        <v>0.545</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.49</v>
+        <v>0.571</v>
       </c>
       <c r="AR48" t="n">
-        <v>0.883</v>
+        <v>0.999</v>
       </c>
       <c r="AS48" t="n">
-        <v>0.099</v>
+        <v>0.125</v>
       </c>
       <c r="AT48" t="n">
-        <v>0.164</v>
+        <v>0.182</v>
       </c>
       <c r="AU48" t="n">
-        <v>0.769</v>
+        <v>1.5</v>
       </c>
       <c r="AV48" t="n">
-        <v>8.462</v>
+        <v>6.286</v>
       </c>
       <c r="AW48" t="n">
-        <v>9.231</v>
+        <v>7.786</v>
       </c>
       <c r="AX48" t="n">
-        <v>0.119</v>
+        <v>0.186</v>
       </c>
       <c r="AY48" t="n">
-        <v>0.024</v>
+        <v>0.124</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0.063</v>
+        <v>0.188</v>
       </c>
       <c r="BA48" t="n">
-        <v>0.019</v>
+        <v>0.052</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>#23 T. JEKIRI (Per Game)</t>
+          <t>#24 B. FERNANDO (Per Game)</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C49" t="n">
-        <v>7.467</v>
+        <v>8.375</v>
       </c>
       <c r="D49" t="n">
-        <v>3.2</v>
+        <v>3.156</v>
       </c>
       <c r="E49" t="n">
-        <v>5.867</v>
+        <v>5.031</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="H49" t="n">
-        <v>1.067</v>
+        <v>1.969</v>
       </c>
       <c r="I49" t="n">
-        <v>1.533</v>
+        <v>2.656</v>
       </c>
       <c r="J49" t="n">
-        <v>1.4</v>
+        <v>0.656</v>
       </c>
       <c r="K49" t="n">
-        <v>2.933</v>
+        <v>2.781</v>
       </c>
       <c r="L49" t="n">
-        <v>2.067</v>
+        <v>1.656</v>
       </c>
       <c r="M49" t="n">
-        <v>0.733</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="N49" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>0.9330000000000001</v>
+        <v>1.625</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.9330000000000001</v>
+        <v>1.625</v>
       </c>
       <c r="R49" t="n">
-        <v>2.533</v>
+        <v>1.875</v>
       </c>
       <c r="S49" t="n">
-        <v>2</v>
+        <v>2.781</v>
       </c>
       <c r="T49" t="n">
-        <v>159</v>
+        <v>367</v>
       </c>
       <c r="U49" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>0.467</v>
+        <v>0.062</v>
       </c>
       <c r="X49" t="n">
-        <v>0.333</v>
+        <v>0.031</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.267</v>
+        <v>4.5</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.8</v>
+        <v>5.594</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.804</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.333</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.2</v>
+        <v>1.25</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.417</v>
+        <v>0.45</v>
       </c>
       <c r="AE49" t="n">
-        <v>0.667</v>
+        <v>0.062</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.156</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.714</v>
+        <v>0.4</v>
       </c>
       <c r="AH49" t="n">
         <v>0</v>
@@ -8193,406 +8193,406 @@
         <v>0</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>37:13</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AO49" t="n">
-        <v>7.475</v>
+        <v>7.888</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.545</v>
+        <v>0.629</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.571</v>
+        <v>0.669</v>
       </c>
       <c r="AR49" t="n">
-        <v>0.999</v>
+        <v>1.062</v>
       </c>
       <c r="AS49" t="n">
-        <v>0.125</v>
+        <v>0.206</v>
       </c>
       <c r="AT49" t="n">
-        <v>0.182</v>
+        <v>0.387</v>
       </c>
       <c r="AU49" t="n">
-        <v>1.5</v>
+        <v>0.404</v>
       </c>
       <c r="AV49" t="n">
-        <v>6.286</v>
+        <v>3.135</v>
       </c>
       <c r="AW49" t="n">
-        <v>7.786</v>
+        <v>3.538</v>
       </c>
       <c r="AX49" t="n">
-        <v>0.096</v>
+        <v>0.206</v>
       </c>
       <c r="AY49" t="n">
-        <v>0.064</v>
+        <v>0.104</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0.097</v>
+        <v>0.186</v>
       </c>
       <c r="BA49" t="n">
-        <v>0.052</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>#24 B. FERNANDO (Per Game)</t>
+          <t>#33 N. CALATHES (Per Game)</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C50" t="n">
-        <v>8.375</v>
+        <v>4.323</v>
       </c>
       <c r="D50" t="n">
-        <v>3.156</v>
+        <v>1.194</v>
       </c>
       <c r="E50" t="n">
-        <v>5.031</v>
+        <v>2.806</v>
       </c>
       <c r="F50" t="n">
-        <v>0.031</v>
+        <v>0.548</v>
       </c>
       <c r="G50" t="n">
+        <v>1.871</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="J50" t="n">
+        <v>4.226</v>
+      </c>
+      <c r="K50" t="n">
+        <v>2.032</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1.452</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1.387</v>
+      </c>
+      <c r="R50" t="n">
+        <v>2.323</v>
+      </c>
+      <c r="S50" t="n">
+        <v>1.129</v>
+      </c>
+      <c r="T50" t="n">
+        <v>194</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>1.548</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.419</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>1.613</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AN50" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
+      <c r="AO50" t="n">
+        <v>6.356</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>0.441</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="AT50" t="n">
         <v>0.062</v>
       </c>
-      <c r="H50" t="n">
-        <v>1.969</v>
-      </c>
-      <c r="I50" t="n">
-        <v>2.656</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0.656</v>
-      </c>
-      <c r="K50" t="n">
-        <v>2.781</v>
-      </c>
-      <c r="L50" t="n">
-        <v>1.656</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>1.625</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>1.625</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1.875</v>
-      </c>
-      <c r="S50" t="n">
-        <v>2.781</v>
-      </c>
-      <c r="T50" t="n">
-        <v>367</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W50" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X50" t="n">
-        <v>0.344</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>5.594</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>0.804</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>0.156</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>36:30</t>
-        </is>
-      </c>
-      <c r="AO50" t="n">
-        <v>7.888</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>0.629</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>0.669</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>1.062</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>0.206</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>0.387</v>
-      </c>
       <c r="AU50" t="n">
-        <v>0.404</v>
+        <v>2.911</v>
       </c>
       <c r="AV50" t="n">
-        <v>3.135</v>
+        <v>3.222</v>
       </c>
       <c r="AW50" t="n">
-        <v>3.538</v>
+        <v>6.133</v>
       </c>
       <c r="AX50" t="n">
-        <v>0.104</v>
+        <v>0.16</v>
       </c>
       <c r="AY50" t="n">
-        <v>0.052</v>
+        <v>0.025</v>
       </c>
       <c r="AZ50" t="n">
-        <v>0.094</v>
+        <v>0.132</v>
       </c>
       <c r="BA50" t="n">
-        <v>0.025</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>#33 N. CALATHES (Per Game)</t>
+          <t>#88 T. JONES (Per Game)</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C51" t="n">
-        <v>4.323</v>
+        <v>10.056</v>
       </c>
       <c r="D51" t="n">
-        <v>1.194</v>
+        <v>4.167</v>
       </c>
       <c r="E51" t="n">
-        <v>2.806</v>
+        <v>6.222</v>
       </c>
       <c r="F51" t="n">
-        <v>0.548</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>1.871</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.29</v>
+        <v>1.722</v>
       </c>
       <c r="I51" t="n">
-        <v>0.516</v>
+        <v>2.667</v>
       </c>
       <c r="J51" t="n">
-        <v>4.226</v>
+        <v>1.944</v>
       </c>
       <c r="K51" t="n">
-        <v>2.032</v>
+        <v>3.5</v>
       </c>
       <c r="L51" t="n">
-        <v>0.419</v>
+        <v>2.278</v>
       </c>
       <c r="M51" t="n">
-        <v>0.871</v>
+        <v>1.167</v>
       </c>
       <c r="N51" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1.444</v>
+      </c>
+      <c r="R51" t="n">
+        <v>2.389</v>
+      </c>
+      <c r="S51" t="n">
+        <v>3.167</v>
+      </c>
+      <c r="T51" t="n">
+        <v>287</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>5.278</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>6.556</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.278</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN51" t="inlineStr">
+        <is>
+          <t>22:17</t>
+        </is>
+      </c>
+      <c r="AO51" t="n">
+        <v>8.896000000000001</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>1.296</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>4.148</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>5.444</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="AZ51" t="n">
         <v>0.194</v>
       </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>1.452</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>1.387</v>
-      </c>
-      <c r="R51" t="n">
-        <v>2.323</v>
-      </c>
-      <c r="S51" t="n">
-        <v>1.129</v>
-      </c>
-      <c r="T51" t="n">
-        <v>194</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0.581</v>
-      </c>
-      <c r="V51" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0.452</v>
-      </c>
-      <c r="X51" t="n">
-        <v>0.258</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>1.548</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0.604</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>0.516</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>1.419</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>0.129</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>0.097</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>0.258</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>0.452</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>1.613</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>41:31</t>
-        </is>
-      </c>
-      <c r="AO51" t="n">
-        <v>6.356</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>0.431</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>0.441</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>0.228</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>2.911</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>3.222</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>6.133</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>0.073</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>0.06</v>
-      </c>
       <c r="BA51" t="n">
-        <v>0.15</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>#88 T. JONES (Per Game)</t>
+          <t>Equip (Per Game)</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C52" t="n">
-        <v>10.056</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>4.167</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>6.222</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -8601,82 +8601,82 @@
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>1.722</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>2.667</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>1.944</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>3.5</v>
+        <v>1.711</v>
       </c>
       <c r="L52" t="n">
-        <v>2.278</v>
+        <v>1.5</v>
       </c>
       <c r="M52" t="n">
-        <v>1.167</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>0.722</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>1.5</v>
+        <v>0.895</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.444</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2.389</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>3.167</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>287</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>0.722</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>2.222</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>0.556</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>0.278</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>5.278</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>6.556</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.805</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.556</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.278</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.435</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0.056</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
         <v>0</v>
@@ -8698,209 +8698,209 @@
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>41:06</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO52" t="n">
-        <v>8.896000000000001</v>
+        <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AS52" t="n">
-        <v>0.169</v>
+        <v>0</v>
       </c>
       <c r="AT52" t="n">
-        <v>0.277</v>
+        <v>0</v>
       </c>
       <c r="AU52" t="n">
-        <v>1.296</v>
+        <v>0</v>
       </c>
       <c r="AV52" t="n">
-        <v>4.148</v>
+        <v>0</v>
       </c>
       <c r="AW52" t="n">
-        <v>5.444</v>
+        <v>0</v>
       </c>
       <c r="AX52" t="n">
-        <v>0.104</v>
+        <v>0</v>
       </c>
       <c r="AY52" t="n">
-        <v>0.064</v>
+        <v>0</v>
       </c>
       <c r="AZ52" t="n">
-        <v>0.105</v>
+        <v>0</v>
       </c>
       <c r="BA52" t="n">
-        <v>0.075</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>TOTAL (Per Game)</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>38</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>81.605</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>39.737</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>8.446999999999999</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>24.763</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>13.263</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>16.368</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>17.474</v>
       </c>
       <c r="K53" t="n">
-        <v>1.711</v>
+        <v>22.737</v>
       </c>
       <c r="L53" t="n">
-        <v>1.5</v>
+        <v>10.289</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>7.105</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>5.158</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>0.895</v>
+        <v>12.5</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>11.105</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>19.184</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>19.132</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>3578</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>0.395</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>0.158</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>0.368</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>0.158</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>27.026</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>34.5</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>0.783</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>6.395</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>0.413</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.342</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>0.447</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.132</v>
       </c>
       <c r="AI53" t="n">
-        <v>0</v>
+        <v>2.684</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>0.422</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>7.316</v>
       </c>
       <c r="AL53" t="n">
-        <v>0</v>
+        <v>22.079</v>
       </c>
       <c r="AM53" t="n">
-        <v>0</v>
+        <v>0.331</v>
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>201:58</t>
         </is>
       </c>
       <c r="AO53" t="n">
-        <v>0</v>
+        <v>84.202</v>
       </c>
       <c r="AP53" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0</v>
+        <v>0.569</v>
       </c>
       <c r="AR53" t="n">
-        <v>0</v>
+        <v>0.969</v>
       </c>
       <c r="AS53" t="n">
-        <v>0</v>
+        <v>0.148</v>
       </c>
       <c r="AT53" t="n">
-        <v>0</v>
+        <v>0.206</v>
       </c>
       <c r="AU53" t="n">
-        <v>0</v>
+        <v>1.398</v>
       </c>
       <c r="AV53" t="n">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="AW53" t="n">
-        <v>0</v>
+        <v>6.558</v>
       </c>
       <c r="AX53" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY53" t="n">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="AZ53" t="n">
-        <v>0</v>
+        <v>0.139</v>
       </c>
       <c r="BA53" t="n">
         <v>0</v>
@@ -8909,495 +8909,165 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>Rival (Per Game)</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>38</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>86.553</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>20.526</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>35.789</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>9.895</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>26.263</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>15.816</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>20.579</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>19.447</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>24.684</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>10.026</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>6.632</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>5.158</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>12.947</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>11.474</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>17.421</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>20.842</v>
       </c>
       <c r="T54" t="n">
-        <v>88</v>
+        <v>4050</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>0.132</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>0.289</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>0.184</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>0.105</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>29.368</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>34.684</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>0.847</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>5.895</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>13.947</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>0.423</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.079</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>2.974</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>0.363</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="AI54" t="n">
-        <v>0</v>
+        <v>1.737</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0</v>
+        <v>0.47</v>
       </c>
       <c r="AK54" t="n">
-        <v>0</v>
+        <v>9.079000000000001</v>
       </c>
       <c r="AL54" t="n">
-        <v>0</v>
+        <v>24.526</v>
       </c>
       <c r="AM54" t="n">
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>201:58</t>
         </is>
       </c>
       <c r="AO54" t="n">
-        <v>0.895</v>
+        <v>84.05500000000001</v>
       </c>
       <c r="AP54" t="n">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0</v>
+        <v>0.609</v>
       </c>
       <c r="AR54" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS54" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="AT54" t="n">
-        <v>0</v>
+        <v>0.255</v>
       </c>
       <c r="AU54" t="n">
-        <v>0</v>
+        <v>1.502</v>
       </c>
       <c r="AV54" t="n">
-        <v>0</v>
+        <v>4.793</v>
       </c>
       <c r="AW54" t="n">
-        <v>0</v>
+        <v>6.295</v>
       </c>
       <c r="AX54" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY54" t="n">
-        <v>0</v>
+        <v>0.057</v>
       </c>
       <c r="AZ54" t="n">
-        <v>0</v>
+        <v>0.151</v>
       </c>
       <c r="BA54" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL (Per Game)</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>38</v>
-      </c>
-      <c r="C55" t="n">
-        <v>81.605</v>
-      </c>
-      <c r="D55" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="E55" t="n">
-        <v>39.737</v>
-      </c>
-      <c r="F55" t="n">
-        <v>8.446999999999999</v>
-      </c>
-      <c r="G55" t="n">
-        <v>24.763</v>
-      </c>
-      <c r="H55" t="n">
-        <v>13.263</v>
-      </c>
-      <c r="I55" t="n">
-        <v>16.368</v>
-      </c>
-      <c r="J55" t="n">
-        <v>17.474</v>
-      </c>
-      <c r="K55" t="n">
-        <v>22.737</v>
-      </c>
-      <c r="L55" t="n">
-        <v>10.289</v>
-      </c>
-      <c r="M55" t="n">
-        <v>7.105</v>
-      </c>
-      <c r="N55" t="n">
-        <v>5.158</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>11.105</v>
-      </c>
-      <c r="R55" t="n">
-        <v>19.184</v>
-      </c>
-      <c r="S55" t="n">
-        <v>19.132</v>
-      </c>
-      <c r="T55" t="n">
-        <v>3578</v>
-      </c>
-      <c r="U55" t="n">
-        <v>10.237</v>
-      </c>
-      <c r="V55" t="n">
-        <v>10.184</v>
-      </c>
-      <c r="W55" t="n">
-        <v>8.079000000000001</v>
-      </c>
-      <c r="X55" t="n">
-        <v>4.447</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>27.026</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>0.783</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>6.395</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>0.413</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>1.342</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>0.447</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>1.132</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>2.684</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>0.422</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>7.316</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>22.079</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>0.331</v>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>201:58</t>
-        </is>
-      </c>
-      <c r="AO55" t="n">
-        <v>84.202</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>0.969</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>0.206</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>1.398</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>6.558</v>
-      </c>
-      <c r="AX55" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY55" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="AZ55" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="BA55" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>Rival (Per Game)</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>38</v>
-      </c>
-      <c r="C56" t="n">
-        <v>86.553</v>
-      </c>
-      <c r="D56" t="n">
-        <v>20.526</v>
-      </c>
-      <c r="E56" t="n">
-        <v>35.789</v>
-      </c>
-      <c r="F56" t="n">
-        <v>9.895</v>
-      </c>
-      <c r="G56" t="n">
-        <v>26.263</v>
-      </c>
-      <c r="H56" t="n">
-        <v>15.816</v>
-      </c>
-      <c r="I56" t="n">
-        <v>20.579</v>
-      </c>
-      <c r="J56" t="n">
-        <v>19.447</v>
-      </c>
-      <c r="K56" t="n">
-        <v>24.684</v>
-      </c>
-      <c r="L56" t="n">
-        <v>10.026</v>
-      </c>
-      <c r="M56" t="n">
-        <v>6.632</v>
-      </c>
-      <c r="N56" t="n">
-        <v>5.158</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>12.947</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>11.526</v>
-      </c>
-      <c r="R56" t="n">
-        <v>17.421</v>
-      </c>
-      <c r="S56" t="n">
-        <v>20.842</v>
-      </c>
-      <c r="T56" t="n">
-        <v>4050</v>
-      </c>
-      <c r="U56" t="n">
-        <v>9.579000000000001</v>
-      </c>
-      <c r="V56" t="n">
-        <v>11.211</v>
-      </c>
-      <c r="W56" t="n">
-        <v>10.816</v>
-      </c>
-      <c r="X56" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>29.368</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>34.684</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>0.847</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>5.895</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>13.947</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>0.423</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>1.079</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>2.974</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>0.363</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>0.8159999999999999</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>1.737</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>9.079000000000001</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>24.526</v>
-      </c>
-      <c r="AM56" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>201:58</t>
-        </is>
-      </c>
-      <c r="AO56" t="n">
-        <v>84.05500000000001</v>
-      </c>
-      <c r="AP56" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="AQ56" t="n">
-        <v>0.609</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="AU56" t="n">
-        <v>1.502</v>
-      </c>
-      <c r="AV56" t="n">
-        <v>4.793</v>
-      </c>
-      <c r="AW56" t="n">
-        <v>6.295</v>
-      </c>
-      <c r="AX56" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY56" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="AZ56" t="n">
-        <v>0.151</v>
-      </c>
-      <c r="BA56" t="n">
         <v>0</v>
       </c>
     </row>

--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_PARTIZAN MOZZART BET BELGRADE.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_PARTIZAN MOZZART BET BELGRADE.xlsx
@@ -671,13 +671,13 @@
         <v>0.2056303549571603</v>
       </c>
       <c r="J2" t="n">
-        <v>15</v>
+        <v>397</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>393</v>
       </c>
       <c r="L2" t="n">
-        <v>14</v>
+        <v>317</v>
       </c>
       <c r="M2" t="n">
         <v>422</v>
@@ -752,13 +752,13 @@
         <v>1.023379383634431</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.03048780487804878</v>
+        <v>0.806910569105691</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.01534526854219949</v>
+        <v>1.005115089514067</v>
       </c>
       <c r="AM2" t="n">
-        <v>2.333333333333333</v>
+        <v>1.780898876404494</v>
       </c>
       <c r="AN2" t="n">
         <v>1.397894736842105</v>
@@ -801,13 +801,13 @@
         <v>0.2056303549571603</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3947368421052632</v>
+        <v>10.44736842105263</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1578947368421053</v>
+        <v>10.3421052631579</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3684210526315789</v>
+        <v>8.342105263157896</v>
       </c>
       <c r="M3" t="n">
         <v>11.10526315789474</v>
@@ -882,13 +882,13 @@
         <v>1.023379383634432</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.03048780487804878</v>
+        <v>0.806910569105691</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.01534526854219949</v>
+        <v>1.005115089514067</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.333333333333333</v>
+        <v>1.780898876404495</v>
       </c>
       <c r="AN3" t="n">
         <v>1.397894736842105</v>
@@ -931,13 +931,13 @@
         <v>0.2548770144189991</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>378</v>
       </c>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>440</v>
       </c>
       <c r="L4" t="n">
-        <v>7</v>
+        <v>420</v>
       </c>
       <c r="M4" t="n">
         <v>436</v>
@@ -1012,13 +1012,13 @@
         <v>1.130260521042084</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.01052631578947368</v>
+        <v>0.7957894736842105</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.02887139107611549</v>
+        <v>1.15485564304462</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.75</v>
+        <v>1.647058823529412</v>
       </c>
       <c r="AN4" t="n">
         <v>1.502032520325203</v>
@@ -1061,13 +1061,13 @@
         <v>0.2548770144189991</v>
       </c>
       <c r="J5" t="n">
-        <v>0.131578947368421</v>
+        <v>9.947368421052632</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2894736842105263</v>
+        <v>11.57894736842105</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1842105263157895</v>
+        <v>11.05263157894737</v>
       </c>
       <c r="M5" t="n">
         <v>11.47368421052632</v>
@@ -1142,13 +1142,13 @@
         <v>1.130260521042084</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.01052631578947368</v>
+        <v>0.7957894736842106</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.02887139107611549</v>
+        <v>1.154855643044619</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.75</v>
+        <v>1.647058823529412</v>
       </c>
       <c r="AN5" t="n">
         <v>1.502032520325203</v>
@@ -1486,16 +1486,16 @@
         <v>282</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Y8" t="n">
         <v>89</v>
@@ -1651,16 +1651,16 @@
         <v>159</v>
       </c>
       <c r="U9" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y9" t="n">
         <v>58</v>
@@ -1819,7 +1819,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -1981,16 +1981,16 @@
         <v>292</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="W11" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Y11" t="n">
         <v>89</v>
@@ -2146,16 +2146,16 @@
         <v>278</v>
       </c>
       <c r="U12" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="V12" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="W12" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="Y12" t="n">
         <v>76</v>
@@ -2317,10 +2317,10 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
         <v>1</v>
@@ -2641,16 +2641,16 @@
         <v>82</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Y15" t="n">
         <v>29</v>
@@ -2971,16 +2971,16 @@
         <v>83</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
         <v>17</v>
@@ -3136,16 +3136,16 @@
         <v>461</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="Y18" t="n">
         <v>115</v>
@@ -3304,13 +3304,13 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
         <v>2</v>
@@ -3466,16 +3466,16 @@
         <v>121</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W20" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y20" t="n">
         <v>36</v>
@@ -3631,16 +3631,16 @@
         <v>563</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="W21" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="Y21" t="n">
         <v>165</v>
@@ -3796,16 +3796,16 @@
         <v>72</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y22" t="n">
         <v>12</v>
@@ -3961,16 +3961,16 @@
         <v>90</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y23" t="n">
         <v>35</v>
@@ -4126,16 +4126,16 @@
         <v>159</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y24" t="n">
         <v>34</v>
@@ -4291,16 +4291,16 @@
         <v>367</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="W25" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y25" t="n">
         <v>144</v>
@@ -4456,16 +4456,16 @@
         <v>194</v>
       </c>
       <c r="U26" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Y26" t="n">
         <v>29</v>
@@ -4621,16 +4621,16 @@
         <v>287</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="V27" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y27" t="n">
         <v>95</v>
@@ -4951,16 +4951,16 @@
         <v>3578</v>
       </c>
       <c r="U29" t="n">
-        <v>15</v>
+        <v>397</v>
       </c>
       <c r="V29" t="n">
-        <v>6</v>
+        <v>393</v>
       </c>
       <c r="W29" t="n">
-        <v>14</v>
+        <v>317</v>
       </c>
       <c r="X29" t="n">
-        <v>6</v>
+        <v>178</v>
       </c>
       <c r="Y29" t="n">
         <v>1027</v>
@@ -5116,16 +5116,16 @@
         <v>4050</v>
       </c>
       <c r="U30" t="n">
-        <v>5</v>
+        <v>378</v>
       </c>
       <c r="V30" t="n">
-        <v>11</v>
+        <v>440</v>
       </c>
       <c r="W30" t="n">
-        <v>7</v>
+        <v>420</v>
       </c>
       <c r="X30" t="n">
-        <v>4</v>
+        <v>255</v>
       </c>
       <c r="Y30" t="n">
         <v>1116</v>
@@ -5340,16 +5340,16 @@
         <v>282</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>2.067</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="Y32" t="n">
         <v>5.933</v>
@@ -5505,16 +5505,16 @@
         <v>159</v>
       </c>
       <c r="U33" t="n">
-        <v>0.167</v>
+        <v>0.917</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="Y33" t="n">
         <v>2.417</v>
@@ -5673,7 +5673,7 @@
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="W34" t="n">
         <v>0</v>
@@ -5835,16 +5835,16 @@
         <v>292</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2.708</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="W35" t="n">
-        <v>0.208</v>
+        <v>1.542</v>
       </c>
       <c r="X35" t="n">
-        <v>0.083</v>
+        <v>0.625</v>
       </c>
       <c r="Y35" t="n">
         <v>3.708</v>
@@ -6000,16 +6000,16 @@
         <v>278</v>
       </c>
       <c r="U36" t="n">
-        <v>0.189</v>
+        <v>0.865</v>
       </c>
       <c r="V36" t="n">
-        <v>0.054</v>
+        <v>1</v>
       </c>
       <c r="W36" t="n">
-        <v>0.081</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="X36" t="n">
-        <v>0.027</v>
+        <v>0.486</v>
       </c>
       <c r="Y36" t="n">
         <v>2.054</v>
@@ -6171,10 +6171,10 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
         <v>1</v>
@@ -6495,16 +6495,16 @@
         <v>82</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>0.579</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.105</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>0.737</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>0.368</v>
       </c>
       <c r="Y39" t="n">
         <v>1.526</v>
@@ -6825,16 +6825,16 @@
         <v>83</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>0.656</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>0.312</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="Y41" t="n">
         <v>0.531</v>
@@ -6990,16 +6990,16 @@
         <v>461</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>2.108</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.432</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.649</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>0.946</v>
       </c>
       <c r="Y42" t="n">
         <v>3.108</v>
@@ -7158,13 +7158,13 @@
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="Y43" t="n">
         <v>0.154</v>
@@ -7320,16 +7320,16 @@
         <v>121</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W44" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="X44" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Y44" t="n">
         <v>3.6</v>
@@ -7485,16 +7485,16 @@
         <v>563</v>
       </c>
       <c r="U45" t="n">
-        <v>0.053</v>
+        <v>1.158</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.711</v>
       </c>
       <c r="W45" t="n">
-        <v>0.053</v>
+        <v>1.316</v>
       </c>
       <c r="X45" t="n">
-        <v>0.026</v>
+        <v>0.895</v>
       </c>
       <c r="Y45" t="n">
         <v>4.342</v>
@@ -7650,16 +7650,16 @@
         <v>72</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>0.188</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>0.094</v>
       </c>
       <c r="Y46" t="n">
         <v>0.375</v>
@@ -7815,16 +7815,16 @@
         <v>90</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>0.579</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>0.316</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>0.368</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>0.211</v>
       </c>
       <c r="Y47" t="n">
         <v>1.842</v>
@@ -7980,16 +7980,16 @@
         <v>159</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.467</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>0.467</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="Y48" t="n">
         <v>2.267</v>
@@ -8145,16 +8145,16 @@
         <v>367</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.531</v>
       </c>
       <c r="W49" t="n">
-        <v>0.062</v>
+        <v>0.5</v>
       </c>
       <c r="X49" t="n">
-        <v>0.031</v>
+        <v>0.344</v>
       </c>
       <c r="Y49" t="n">
         <v>4.5</v>
@@ -8310,16 +8310,16 @@
         <v>194</v>
       </c>
       <c r="U50" t="n">
-        <v>0.065</v>
+        <v>0.581</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>0.548</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="Y50" t="n">
         <v>0.9350000000000001</v>
@@ -8475,16 +8475,16 @@
         <v>287</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>0.722</v>
       </c>
       <c r="V51" t="n">
-        <v>0.111</v>
+        <v>2.389</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>0.556</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>0.278</v>
       </c>
       <c r="Y51" t="n">
         <v>5.278</v>
@@ -8805,16 +8805,16 @@
         <v>3578</v>
       </c>
       <c r="U53" t="n">
-        <v>0.395</v>
+        <v>10.447</v>
       </c>
       <c r="V53" t="n">
-        <v>0.158</v>
+        <v>10.342</v>
       </c>
       <c r="W53" t="n">
-        <v>0.368</v>
+        <v>8.342000000000001</v>
       </c>
       <c r="X53" t="n">
-        <v>0.158</v>
+        <v>4.684</v>
       </c>
       <c r="Y53" t="n">
         <v>27.026</v>
@@ -8970,16 +8970,16 @@
         <v>4050</v>
       </c>
       <c r="U54" t="n">
-        <v>0.132</v>
+        <v>9.946999999999999</v>
       </c>
       <c r="V54" t="n">
-        <v>0.289</v>
+        <v>11.579</v>
       </c>
       <c r="W54" t="n">
-        <v>0.184</v>
+        <v>11.053</v>
       </c>
       <c r="X54" t="n">
-        <v>0.105</v>
+        <v>6.711</v>
       </c>
       <c r="Y54" t="n">
         <v>29.368</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_PARTIZAN MOZZART BET BELGRADE.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_PARTIZAN MOZZART BET BELGRADE.xlsx
@@ -683,13 +683,13 @@
         <v>422</v>
       </c>
       <c r="N2" t="n">
-        <v>1027</v>
+        <v>523</v>
       </c>
       <c r="O2" t="n">
-        <v>1311</v>
+        <v>807</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.3292533659730722</v>
       </c>
       <c r="Q2" t="n">
         <v>243</v>
@@ -710,25 +710,25 @@
         <v>0.04651162790697674</v>
       </c>
       <c r="W2" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="X2" t="n">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0416156670746634</v>
+        <v>0.05671154630762954</v>
       </c>
       <c r="Z2" t="n">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="AA2" t="n">
-        <v>839</v>
+        <v>802</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3423092615259078</v>
+        <v>0.3272133822929417</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7833714721586575</v>
+        <v>0.6480793060718711</v>
       </c>
       <c r="AD2" t="n">
         <v>0.4125636672325976</v>
@@ -737,13 +737,13 @@
         <v>0.4473684210526316</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.4215686274509804</v>
+        <v>0.4028776978417266</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.33134684147795</v>
+        <v>0.3304239401496259</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.566742944317315</v>
+        <v>1.296158612143742</v>
       </c>
       <c r="AI2" t="n">
         <v>0.8947368421052632</v>
@@ -813,13 +813,13 @@
         <v>11.10526315789474</v>
       </c>
       <c r="N3" t="n">
-        <v>27.02631578947368</v>
+        <v>13.76315789473684</v>
       </c>
       <c r="O3" t="n">
-        <v>34.5</v>
+        <v>21.23684210526316</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.3292533659730722</v>
       </c>
       <c r="Q3" t="n">
         <v>6.394736842105263</v>
@@ -840,25 +840,25 @@
         <v>0.04651162790697674</v>
       </c>
       <c r="W3" t="n">
-        <v>1.131578947368421</v>
+        <v>1.473684210526316</v>
       </c>
       <c r="X3" t="n">
-        <v>2.684210526315789</v>
+        <v>3.657894736842105</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0416156670746634</v>
+        <v>0.05671154630762954</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.315789473684211</v>
+        <v>6.973684210526316</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.07894736842105</v>
+        <v>21.10526315789474</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3423092615259078</v>
+        <v>0.3272133822929417</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7833714721586575</v>
+        <v>0.6480793060718711</v>
       </c>
       <c r="AD3" t="n">
         <v>0.4125636672325976</v>
@@ -867,13 +867,13 @@
         <v>0.4473684210526316</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.4215686274509804</v>
+        <v>0.4028776978417266</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.33134684147795</v>
+        <v>0.3304239401496259</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.566742944317315</v>
+        <v>1.296158612143742</v>
       </c>
       <c r="AI3" t="n">
         <v>0.8947368421052632</v>
@@ -943,13 +943,13 @@
         <v>436</v>
       </c>
       <c r="N4" t="n">
-        <v>1116</v>
+        <v>515</v>
       </c>
       <c r="O4" t="n">
-        <v>1318</v>
+        <v>717</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5589482612383376</v>
+        <v>0.3040712468193384</v>
       </c>
       <c r="Q4" t="n">
         <v>224</v>
@@ -970,25 +970,25 @@
         <v>0.04792196776929601</v>
       </c>
       <c r="W4" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="X4" t="n">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.02798982188295165</v>
+        <v>0.04240882103477523</v>
       </c>
       <c r="Z4" t="n">
-        <v>345</v>
+        <v>328</v>
       </c>
       <c r="AA4" t="n">
-        <v>932</v>
+        <v>898</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3952502120441052</v>
+        <v>0.3808312128922816</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.8467374810318664</v>
+        <v>0.7182705718270572</v>
       </c>
       <c r="AD4" t="n">
         <v>0.4226415094339623</v>
@@ -997,13 +997,13 @@
         <v>0.3628318584070797</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.4696969696969697</v>
+        <v>0.48</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3701716738197425</v>
+        <v>0.3652561247216036</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.693474962063733</v>
+        <v>1.436541143654114</v>
       </c>
       <c r="AI4" t="n">
         <v>0.7256637168141593</v>
@@ -1073,13 +1073,13 @@
         <v>11.47368421052632</v>
       </c>
       <c r="N5" t="n">
-        <v>29.36842105263158</v>
+        <v>13.55263157894737</v>
       </c>
       <c r="O5" t="n">
-        <v>34.68421052631579</v>
+        <v>18.86842105263158</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5589482612383375</v>
+        <v>0.3040712468193384</v>
       </c>
       <c r="Q5" t="n">
         <v>5.894736842105263</v>
@@ -1100,25 +1100,25 @@
         <v>0.04792196776929601</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8157894736842105</v>
+        <v>1.263157894736842</v>
       </c>
       <c r="X5" t="n">
-        <v>1.736842105263158</v>
+        <v>2.631578947368421</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.02798982188295165</v>
+        <v>0.04240882103477524</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.078947368421053</v>
+        <v>8.631578947368421</v>
       </c>
       <c r="AA5" t="n">
-        <v>24.52631578947368</v>
+        <v>23.63157894736842</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3952502120441052</v>
+        <v>0.3808312128922816</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.8467374810318665</v>
+        <v>0.7182705718270572</v>
       </c>
       <c r="AD5" t="n">
         <v>0.4226415094339622</v>
@@ -1127,13 +1127,13 @@
         <v>0.3628318584070797</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.4696969696969697</v>
+        <v>0.4799999999999999</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3701716738197425</v>
+        <v>0.3652561247216036</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.693474962063733</v>
+        <v>1.436541143654114</v>
       </c>
       <c r="AI5" t="n">
         <v>0.7256637168141593</v>
@@ -1498,13 +1498,13 @@
         <v>11</v>
       </c>
       <c r="Y8" t="n">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="Z8" t="n">
-        <v>111</v>
+        <v>56</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.802</v>
+        <v>0.607</v>
       </c>
       <c r="AB8" t="n">
         <v>28</v>
@@ -1528,7 +1528,7 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>12</v>
       </c>
       <c r="AL8" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.308</v>
+        <v>0.316</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
@@ -1663,13 +1663,13 @@
         <v>8</v>
       </c>
       <c r="Y9" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="Z9" t="n">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.744</v>
+        <v>0.556</v>
       </c>
       <c r="AB9" t="n">
         <v>23</v>
@@ -1690,22 +1690,22 @@
         <v>0.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AK9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL9" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.273</v>
+        <v>0.267</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
@@ -1828,13 +1828,13 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1993,13 +1993,13 @@
         <v>15</v>
       </c>
       <c r="Y11" t="n">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="Z11" t="n">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.754</v>
+        <v>0.608</v>
       </c>
       <c r="AB11" t="n">
         <v>23</v>
@@ -2023,19 +2023,19 @@
         <v>3</v>
       </c>
       <c r="AI11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.375</v>
+        <v>0.333</v>
       </c>
       <c r="AK11" t="n">
         <v>46</v>
       </c>
       <c r="AL11" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.377</v>
+        <v>0.38</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
@@ -2158,13 +2158,13 @@
         <v>18</v>
       </c>
       <c r="Y12" t="n">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="Z12" t="n">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.768</v>
+        <v>0.623</v>
       </c>
       <c r="AB12" t="n">
         <v>9</v>
@@ -2185,22 +2185,22 @@
         <v>0.429</v>
       </c>
       <c r="AH12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.389</v>
+        <v>0.381</v>
       </c>
       <c r="AK12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AL12" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.352</v>
+        <v>0.353</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
@@ -2653,13 +2653,13 @@
         <v>7</v>
       </c>
       <c r="Y15" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="Z15" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.763</v>
+        <v>0.625</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -2683,19 +2683,19 @@
         <v>1</v>
       </c>
       <c r="AI15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="AK15" t="n">
         <v>22</v>
       </c>
       <c r="AL15" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.338</v>
+        <v>0.349</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
@@ -2983,13 +2983,13 @@
         <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Z17" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.68</v>
+        <v>0.636</v>
       </c>
       <c r="AB17" t="n">
         <v>11</v>
@@ -3148,13 +3148,13 @@
         <v>35</v>
       </c>
       <c r="Y18" t="n">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="Z18" t="n">
-        <v>157</v>
+        <v>100</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.732</v>
+        <v>0.58</v>
       </c>
       <c r="AB18" t="n">
         <v>42</v>
@@ -3175,22 +3175,22 @@
         <v>0.44</v>
       </c>
       <c r="AH18" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AI18" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="AK18" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="AL18" t="n">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.36</v>
+        <v>0.342</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
@@ -3478,13 +3478,13 @@
         <v>10</v>
       </c>
       <c r="Y20" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="Z20" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.857</v>
+        <v>0.647</v>
       </c>
       <c r="AB20" t="n">
         <v>5</v>
@@ -3643,13 +3643,13 @@
         <v>34</v>
       </c>
       <c r="Y21" t="n">
-        <v>165</v>
+        <v>74</v>
       </c>
       <c r="Z21" t="n">
-        <v>190</v>
+        <v>99</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.868</v>
+        <v>0.747</v>
       </c>
       <c r="AB21" t="n">
         <v>22</v>
@@ -3670,22 +3670,22 @@
         <v>0.333</v>
       </c>
       <c r="AH21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AI21" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.556</v>
+        <v>0.4</v>
       </c>
       <c r="AK21" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL21" t="n">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.286</v>
+        <v>0.288</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
@@ -3808,13 +3808,13 @@
         <v>3</v>
       </c>
       <c r="Y22" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z22" t="n">
         <v>12</v>
       </c>
-      <c r="Z22" t="n">
-        <v>18</v>
-      </c>
       <c r="AA22" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="AB22" t="n">
         <v>3</v>
@@ -3838,19 +3838,19 @@
         <v>1</v>
       </c>
       <c r="AI22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AK22" t="n">
         <v>14</v>
       </c>
       <c r="AL22" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.359</v>
+        <v>0.368</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
@@ -3973,13 +3973,13 @@
         <v>4</v>
       </c>
       <c r="Y23" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="Z23" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.795</v>
+        <v>0.654</v>
       </c>
       <c r="AB23" t="n">
         <v>12</v>
@@ -4000,22 +4000,22 @@
         <v>0.333</v>
       </c>
       <c r="AH23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AK23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL23" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.222</v>
+        <v>0.226</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
@@ -4138,13 +4138,13 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="Z24" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AB24" t="n">
         <v>20</v>
@@ -4303,13 +4303,13 @@
         <v>11</v>
       </c>
       <c r="Y25" t="n">
-        <v>144</v>
+        <v>81</v>
       </c>
       <c r="Z25" t="n">
-        <v>179</v>
+        <v>116</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.804</v>
+        <v>0.698</v>
       </c>
       <c r="AB25" t="n">
         <v>18</v>
@@ -4468,13 +4468,13 @@
         <v>9</v>
       </c>
       <c r="Y26" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="Z26" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.604</v>
+        <v>0.513</v>
       </c>
       <c r="AB26" t="n">
         <v>16</v>
@@ -4495,22 +4495,22 @@
         <v>0.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.375</v>
+        <v>0.444</v>
       </c>
       <c r="AK26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL26" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.28</v>
+        <v>0.265</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>5</v>
       </c>
       <c r="Y27" t="n">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="Z27" t="n">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.805</v>
+        <v>0.736</v>
       </c>
       <c r="AB27" t="n">
         <v>10</v>
@@ -4963,13 +4963,13 @@
         <v>178</v>
       </c>
       <c r="Y29" t="n">
-        <v>1027</v>
+        <v>523</v>
       </c>
       <c r="Z29" t="n">
-        <v>1311</v>
+        <v>807</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.783</v>
+        <v>0.648</v>
       </c>
       <c r="AB29" t="n">
         <v>243</v>
@@ -4990,22 +4990,22 @@
         <v>0.447</v>
       </c>
       <c r="AH29" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="AI29" t="n">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.422</v>
+        <v>0.403</v>
       </c>
       <c r="AK29" t="n">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="AL29" t="n">
-        <v>839</v>
+        <v>802</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.331</v>
+        <v>0.33</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
@@ -5128,13 +5128,13 @@
         <v>255</v>
       </c>
       <c r="Y30" t="n">
-        <v>1116</v>
+        <v>515</v>
       </c>
       <c r="Z30" t="n">
-        <v>1318</v>
+        <v>717</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.847</v>
+        <v>0.718</v>
       </c>
       <c r="AB30" t="n">
         <v>224</v>
@@ -5155,22 +5155,22 @@
         <v>0.363</v>
       </c>
       <c r="AH30" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="AI30" t="n">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="AK30" t="n">
-        <v>345</v>
+        <v>328</v>
       </c>
       <c r="AL30" t="n">
-        <v>932</v>
+        <v>898</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.37</v>
+        <v>0.365</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
@@ -5352,13 +5352,13 @@
         <v>0.733</v>
       </c>
       <c r="Y32" t="n">
-        <v>5.933</v>
+        <v>2.267</v>
       </c>
       <c r="Z32" t="n">
-        <v>7.4</v>
+        <v>3.733</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.802</v>
+        <v>0.607</v>
       </c>
       <c r="AB32" t="n">
         <v>1.867</v>
@@ -5382,7 +5382,7 @@
         <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.2</v>
+        <v>0.267</v>
       </c>
       <c r="AJ32" t="n">
         <v>0</v>
@@ -5391,10 +5391,10 @@
         <v>0.8</v>
       </c>
       <c r="AL32" t="n">
-        <v>2.6</v>
+        <v>2.533</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.308</v>
+        <v>0.316</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
@@ -5517,13 +5517,13 @@
         <v>0.333</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.417</v>
+        <v>1.042</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.25</v>
+        <v>1.875</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.744</v>
+        <v>0.556</v>
       </c>
       <c r="AB33" t="n">
         <v>0.958</v>
@@ -5544,22 +5544,22 @@
         <v>0.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.083</v>
+        <v>0.208</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.375</v>
+        <v>0.333</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.375</v>
+        <v>1.25</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.273</v>
+        <v>0.267</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
@@ -5682,13 +5682,13 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.062</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.062</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
@@ -5847,13 +5847,13 @@
         <v>0.625</v>
       </c>
       <c r="Y35" t="n">
-        <v>3.708</v>
+        <v>1.875</v>
       </c>
       <c r="Z35" t="n">
-        <v>4.917</v>
+        <v>3.083</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.754</v>
+        <v>0.608</v>
       </c>
       <c r="AB35" t="n">
         <v>0.958</v>
@@ -5877,19 +5877,19 @@
         <v>0.125</v>
       </c>
       <c r="AI35" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AJ35" t="n">
         <v>0.333</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0.375</v>
       </c>
       <c r="AK35" t="n">
         <v>1.917</v>
       </c>
       <c r="AL35" t="n">
-        <v>5.083</v>
+        <v>5.042</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.377</v>
+        <v>0.38</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
@@ -6012,13 +6012,13 @@
         <v>0.486</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.054</v>
+        <v>1.027</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.676</v>
+        <v>1.649</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.768</v>
+        <v>0.623</v>
       </c>
       <c r="AB36" t="n">
         <v>0.243</v>
@@ -6039,22 +6039,22 @@
         <v>0.429</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.189</v>
+        <v>0.216</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.486</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.389</v>
+        <v>0.381</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.838</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="AL36" t="n">
-        <v>2.378</v>
+        <v>2.297</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.352</v>
+        <v>0.353</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
@@ -6507,13 +6507,13 @@
         <v>0.368</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.526</v>
+        <v>0.789</v>
       </c>
       <c r="Z39" t="n">
-        <v>2</v>
+        <v>1.263</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.763</v>
+        <v>0.625</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
@@ -6537,19 +6537,19 @@
         <v>0.053</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.211</v>
+        <v>0.316</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="AK39" t="n">
         <v>1.158</v>
       </c>
       <c r="AL39" t="n">
-        <v>3.421</v>
+        <v>3.316</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.338</v>
+        <v>0.349</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
@@ -6837,13 +6837,13 @@
         <v>0.031</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.531</v>
+        <v>0.438</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.781</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.68</v>
+        <v>0.636</v>
       </c>
       <c r="AB41" t="n">
         <v>0.344</v>
@@ -7002,13 +7002,13 @@
         <v>0.946</v>
       </c>
       <c r="Y42" t="n">
-        <v>3.108</v>
+        <v>1.568</v>
       </c>
       <c r="Z42" t="n">
-        <v>4.243</v>
+        <v>2.703</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.732</v>
+        <v>0.58</v>
       </c>
       <c r="AB42" t="n">
         <v>1.135</v>
@@ -7029,22 +7029,22 @@
         <v>0.44</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.459</v>
+        <v>0.622</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.8110000000000001</v>
+        <v>1.054</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.595</v>
+        <v>1.432</v>
       </c>
       <c r="AL42" t="n">
-        <v>4.432</v>
+        <v>4.189</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.36</v>
+        <v>0.342</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
@@ -7332,13 +7332,13 @@
         <v>1</v>
       </c>
       <c r="Y44" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="Z44" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.857</v>
+        <v>0.647</v>
       </c>
       <c r="AB44" t="n">
         <v>0.5</v>
@@ -7497,13 +7497,13 @@
         <v>0.895</v>
       </c>
       <c r="Y45" t="n">
-        <v>4.342</v>
+        <v>1.947</v>
       </c>
       <c r="Z45" t="n">
-        <v>5</v>
+        <v>2.605</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.868</v>
+        <v>0.747</v>
       </c>
       <c r="AB45" t="n">
         <v>0.579</v>
@@ -7524,22 +7524,22 @@
         <v>0.333</v>
       </c>
       <c r="AH45" t="n">
-        <v>0.132</v>
+        <v>0.211</v>
       </c>
       <c r="AI45" t="n">
-        <v>0.237</v>
+        <v>0.526</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.556</v>
+        <v>0.4</v>
       </c>
       <c r="AK45" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.605</v>
       </c>
       <c r="AL45" t="n">
-        <v>2.395</v>
+        <v>2.105</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.286</v>
+        <v>0.288</v>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
@@ -7662,13 +7662,13 @@
         <v>0.094</v>
       </c>
       <c r="Y46" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="Z46" t="n">
         <v>0.375</v>
       </c>
-      <c r="Z46" t="n">
-        <v>0.5620000000000001</v>
-      </c>
       <c r="AA46" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="AB46" t="n">
         <v>0.094</v>
@@ -7692,19 +7692,19 @@
         <v>0.031</v>
       </c>
       <c r="AI46" t="n">
-        <v>0.125</v>
+        <v>0.156</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AK46" t="n">
         <v>0.438</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.219</v>
+        <v>1.188</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.359</v>
+        <v>0.368</v>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
@@ -7827,13 +7827,13 @@
         <v>0.211</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.842</v>
+        <v>0.895</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.316</v>
+        <v>1.368</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.795</v>
+        <v>0.654</v>
       </c>
       <c r="AB47" t="n">
         <v>0.632</v>
@@ -7854,22 +7854,22 @@
         <v>0.333</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.211</v>
+        <v>0.263</v>
       </c>
       <c r="AI47" t="n">
-        <v>0.263</v>
+        <v>0.526</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AK47" t="n">
-        <v>0.421</v>
+        <v>0.368</v>
       </c>
       <c r="AL47" t="n">
-        <v>1.895</v>
+        <v>1.632</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.222</v>
+        <v>0.226</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
@@ -7992,13 +7992,13 @@
         <v>0.333</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.267</v>
+        <v>1.2</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.8</v>
+        <v>1.733</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AB48" t="n">
         <v>1.333</v>
@@ -8157,13 +8157,13 @@
         <v>0.344</v>
       </c>
       <c r="Y49" t="n">
-        <v>4.5</v>
+        <v>2.531</v>
       </c>
       <c r="Z49" t="n">
-        <v>5.594</v>
+        <v>3.625</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.804</v>
+        <v>0.698</v>
       </c>
       <c r="AB49" t="n">
         <v>0.5620000000000001</v>
@@ -8322,13 +8322,13 @@
         <v>0.29</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.645</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.548</v>
+        <v>1.258</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.604</v>
+        <v>0.513</v>
       </c>
       <c r="AB50" t="n">
         <v>0.516</v>
@@ -8349,22 +8349,22 @@
         <v>0.25</v>
       </c>
       <c r="AH50" t="n">
-        <v>0.097</v>
+        <v>0.129</v>
       </c>
       <c r="AI50" t="n">
-        <v>0.258</v>
+        <v>0.29</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.375</v>
+        <v>0.444</v>
       </c>
       <c r="AK50" t="n">
-        <v>0.452</v>
+        <v>0.419</v>
       </c>
       <c r="AL50" t="n">
-        <v>1.613</v>
+        <v>1.581</v>
       </c>
       <c r="AM50" t="n">
-        <v>0.28</v>
+        <v>0.265</v>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
@@ -8487,13 +8487,13 @@
         <v>0.278</v>
       </c>
       <c r="Y51" t="n">
-        <v>5.278</v>
+        <v>3.556</v>
       </c>
       <c r="Z51" t="n">
-        <v>6.556</v>
+        <v>4.833</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.805</v>
+        <v>0.736</v>
       </c>
       <c r="AB51" t="n">
         <v>0.556</v>
@@ -8817,13 +8817,13 @@
         <v>4.684</v>
       </c>
       <c r="Y53" t="n">
-        <v>27.026</v>
+        <v>13.763</v>
       </c>
       <c r="Z53" t="n">
-        <v>34.5</v>
+        <v>21.237</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.783</v>
+        <v>0.648</v>
       </c>
       <c r="AB53" t="n">
         <v>6.395</v>
@@ -8844,22 +8844,22 @@
         <v>0.447</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.132</v>
+        <v>1.474</v>
       </c>
       <c r="AI53" t="n">
-        <v>2.684</v>
+        <v>3.658</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0.422</v>
+        <v>0.403</v>
       </c>
       <c r="AK53" t="n">
-        <v>7.316</v>
+        <v>6.974</v>
       </c>
       <c r="AL53" t="n">
-        <v>22.079</v>
+        <v>21.105</v>
       </c>
       <c r="AM53" t="n">
-        <v>0.331</v>
+        <v>0.33</v>
       </c>
       <c r="AN53" t="inlineStr">
         <is>
@@ -8982,13 +8982,13 @@
         <v>6.711</v>
       </c>
       <c r="Y54" t="n">
-        <v>29.368</v>
+        <v>13.553</v>
       </c>
       <c r="Z54" t="n">
-        <v>34.684</v>
+        <v>18.868</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.847</v>
+        <v>0.718</v>
       </c>
       <c r="AB54" t="n">
         <v>5.895</v>
@@ -9009,22 +9009,22 @@
         <v>0.363</v>
       </c>
       <c r="AH54" t="n">
-        <v>0.8159999999999999</v>
+        <v>1.263</v>
       </c>
       <c r="AI54" t="n">
-        <v>1.737</v>
+        <v>2.632</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="AK54" t="n">
-        <v>9.079000000000001</v>
+        <v>8.632</v>
       </c>
       <c r="AL54" t="n">
-        <v>24.526</v>
+        <v>23.632</v>
       </c>
       <c r="AM54" t="n">
-        <v>0.37</v>
+        <v>0.365</v>
       </c>
       <c r="AN54" t="inlineStr">
         <is>
